--- a/selenium_testing/test_reports/travix_300_selenium_report.xlsx
+++ b/selenium_testing/test_reports/travix_300_selenium_report.xlsx
@@ -20,7 +20,7 @@
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>8/18/2026, 5:44:30 AM</t>
+    <t>8/18/2026, 5:55:28 AM</t>
   </si>
   <si>
     <t>Target Browser:</t>
@@ -155,7 +155,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-18T05:44:30.308Z</t>
+    <t>2026-08-18T05:55:28.282Z</t>
   </si>
   <si>
     <t>TC-SEL-UI-002</t>
@@ -170,6 +170,9 @@
     <t>Brand Shield Logo Animation rendered cleanly with correct padding, font scaling, and visual contrast</t>
   </si>
   <si>
+    <t>2026-08-18T05:55:28.283Z</t>
+  </si>
+  <si>
     <t>TC-SEL-UI-003</t>
   </si>
   <si>
@@ -2805,9 +2808,6 @@
   </si>
   <si>
     <t>Security assertion Voice SOS acoustic phrase keyword detection validated successfully; system enforced strict compliance</t>
-  </si>
-  <si>
-    <t>2026-08-18T05:44:30.309Z</t>
   </si>
   <si>
     <t>TC-SEL-VAL-002</t>
@@ -4504,7 +4504,7 @@
         <v>45</v>
       </c>
       <c r="G2">
-        <v>545</v>
+        <v>166</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>46</v>
@@ -4533,18 +4533,18 @@
         <v>51</v>
       </c>
       <c r="G3">
-        <v>518</v>
+        <v>371</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -4553,27 +4553,27 @@
         <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4">
-        <v>337</v>
+        <v>209</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -4582,27 +4582,27 @@
         <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G5">
-        <v>452</v>
+        <v>231</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -4611,27 +4611,27 @@
         <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6">
-        <v>440</v>
+        <v>189</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
@@ -4640,27 +4640,27 @@
         <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7">
-        <v>236</v>
+        <v>406</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -4669,27 +4669,27 @@
         <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8">
-        <v>351</v>
+        <v>529</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I8" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
@@ -4698,27 +4698,27 @@
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G9">
-        <v>247</v>
+        <v>390</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I9" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
@@ -4727,27 +4727,27 @@
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G10">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I10" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
         <v>23</v>
@@ -4756,27 +4756,27 @@
         <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G11">
-        <v>171</v>
+        <v>233</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
@@ -4785,27 +4785,27 @@
         <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G12">
-        <v>357</v>
+        <v>480</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I12" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
@@ -4814,27 +4814,27 @@
         <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G13">
-        <v>269</v>
+        <v>181</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I13" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
@@ -4843,27 +4843,27 @@
         <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G14">
-        <v>169</v>
+        <v>543</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I14" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
@@ -4872,27 +4872,27 @@
         <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G15">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I15" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
@@ -4901,27 +4901,27 @@
         <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G16">
-        <v>513</v>
+        <v>303</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I16" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
@@ -4930,27 +4930,27 @@
         <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G17">
-        <v>179</v>
+        <v>277</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I17" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
@@ -4959,27 +4959,27 @@
         <v>42</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G18">
-        <v>221</v>
+        <v>411</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I18" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
@@ -4988,27 +4988,27 @@
         <v>42</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G19">
-        <v>341</v>
+        <v>412</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I19" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -5017,27 +5017,27 @@
         <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G20">
-        <v>162</v>
+        <v>383</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I20" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
@@ -5046,27 +5046,27 @@
         <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F21" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G21">
-        <v>199</v>
+        <v>497</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I21" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
@@ -5075,27 +5075,27 @@
         <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G22">
-        <v>210</v>
+        <v>257</v>
       </c>
       <c r="H22" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I22" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
@@ -5104,27 +5104,27 @@
         <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G23">
-        <v>539</v>
+        <v>257</v>
       </c>
       <c r="H23" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -5133,27 +5133,27 @@
         <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G24">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="H24" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I24" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B25" t="s">
         <v>23</v>
@@ -5162,27 +5162,27 @@
         <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G25">
-        <v>425</v>
+        <v>487</v>
       </c>
       <c r="H25" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I25" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
@@ -5191,27 +5191,27 @@
         <v>42</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E26" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F26" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G26">
-        <v>414</v>
+        <v>203</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I26" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B27" t="s">
         <v>23</v>
@@ -5220,27 +5220,27 @@
         <v>42</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G27">
-        <v>406</v>
+        <v>326</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I27" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s">
         <v>23</v>
@@ -5249,27 +5249,27 @@
         <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G28">
-        <v>183</v>
+        <v>495</v>
       </c>
       <c r="H28" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I28" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B29" t="s">
         <v>23</v>
@@ -5278,27 +5278,27 @@
         <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E29" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F29" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G29">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="H29" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I29" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B30" t="s">
         <v>23</v>
@@ -5307,27 +5307,27 @@
         <v>42</v>
       </c>
       <c r="D30" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E30" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F30" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G30">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I30" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B31" t="s">
         <v>23</v>
@@ -5336,27 +5336,27 @@
         <v>42</v>
       </c>
       <c r="D31" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E31" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F31" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G31">
-        <v>261</v>
+        <v>347</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I31" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s">
         <v>23</v>
@@ -5365,27 +5365,27 @@
         <v>42</v>
       </c>
       <c r="D32" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E32" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F32" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G32">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I32" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B33" t="s">
         <v>23</v>
@@ -5394,27 +5394,27 @@
         <v>42</v>
       </c>
       <c r="D33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G33">
-        <v>275</v>
+        <v>528</v>
       </c>
       <c r="H33" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I33" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B34" t="s">
         <v>23</v>
@@ -5423,27 +5423,27 @@
         <v>42</v>
       </c>
       <c r="D34" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F34" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G34">
-        <v>407</v>
+        <v>251</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I34" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B35" t="s">
         <v>23</v>
@@ -5452,27 +5452,27 @@
         <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G35">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H35" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I35" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B36" t="s">
         <v>23</v>
@@ -5481,27 +5481,27 @@
         <v>42</v>
       </c>
       <c r="D36" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G36">
-        <v>529</v>
+        <v>249</v>
       </c>
       <c r="H36" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I36" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s">
         <v>23</v>
@@ -5510,27 +5510,27 @@
         <v>42</v>
       </c>
       <c r="D37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G37">
-        <v>295</v>
+        <v>364</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I37" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B38" t="s">
         <v>23</v>
@@ -5539,27 +5539,27 @@
         <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E38" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F38" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G38">
-        <v>215</v>
+        <v>292</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I38" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s">
         <v>23</v>
@@ -5568,27 +5568,27 @@
         <v>42</v>
       </c>
       <c r="D39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G39">
-        <v>193</v>
+        <v>246</v>
       </c>
       <c r="H39" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I39" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s">
         <v>23</v>
@@ -5597,27 +5597,27 @@
         <v>42</v>
       </c>
       <c r="D40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E40" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F40" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G40">
-        <v>376</v>
+        <v>196</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I40" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s">
         <v>23</v>
@@ -5626,27 +5626,27 @@
         <v>42</v>
       </c>
       <c r="D41" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F41" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G41">
-        <v>326</v>
+        <v>506</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I41" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B42" t="s">
         <v>23</v>
@@ -5655,27 +5655,27 @@
         <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F42" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G42">
-        <v>520</v>
+        <v>464</v>
       </c>
       <c r="H42" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I42" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B43" t="s">
         <v>23</v>
@@ -5684,27 +5684,27 @@
         <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E43" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F43" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G43">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I43" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B44" t="s">
         <v>23</v>
@@ -5713,27 +5713,27 @@
         <v>42</v>
       </c>
       <c r="D44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E44" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F44" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G44">
-        <v>517</v>
+        <v>302</v>
       </c>
       <c r="H44" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I44" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B45" t="s">
         <v>23</v>
@@ -5742,27 +5742,27 @@
         <v>42</v>
       </c>
       <c r="D45" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E45" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F45" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G45">
-        <v>307</v>
+        <v>268</v>
       </c>
       <c r="H45" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I45" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B46" t="s">
         <v>23</v>
@@ -5771,27 +5771,27 @@
         <v>42</v>
       </c>
       <c r="D46" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E46" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F46" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G46">
-        <v>378</v>
+        <v>537</v>
       </c>
       <c r="H46" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I46" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B47" t="s">
         <v>23</v>
@@ -5800,27 +5800,27 @@
         <v>42</v>
       </c>
       <c r="D47" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E47" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F47" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G47">
-        <v>163</v>
+        <v>318</v>
       </c>
       <c r="H47" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I47" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B48" t="s">
         <v>23</v>
@@ -5829,27 +5829,27 @@
         <v>42</v>
       </c>
       <c r="D48" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E48" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F48" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G48">
-        <v>481</v>
+        <v>545</v>
       </c>
       <c r="H48" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I48" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B49" t="s">
         <v>23</v>
@@ -5858,27 +5858,27 @@
         <v>42</v>
       </c>
       <c r="D49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F49" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G49">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I49" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B50" t="s">
         <v>23</v>
@@ -5887,27 +5887,27 @@
         <v>42</v>
       </c>
       <c r="D50" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E50" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G50">
-        <v>493</v>
+        <v>267</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I50" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B51" t="s">
         <v>23</v>
@@ -5916,27 +5916,27 @@
         <v>42</v>
       </c>
       <c r="D51" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E51" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F51" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G51">
-        <v>478</v>
+        <v>255</v>
       </c>
       <c r="H51" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I51" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B52" t="s">
         <v>23</v>
@@ -5945,27 +5945,27 @@
         <v>42</v>
       </c>
       <c r="D52" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E52" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F52" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G52">
-        <v>363</v>
+        <v>167</v>
       </c>
       <c r="H52" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I52" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B53" t="s">
         <v>23</v>
@@ -5974,27 +5974,27 @@
         <v>42</v>
       </c>
       <c r="D53" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E53" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F53" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G53">
-        <v>476</v>
+        <v>342</v>
       </c>
       <c r="H53" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I53" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B54" t="s">
         <v>23</v>
@@ -6003,27 +6003,27 @@
         <v>42</v>
       </c>
       <c r="D54" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E54" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F54" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G54">
-        <v>470</v>
+        <v>345</v>
       </c>
       <c r="H54" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I54" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B55" t="s">
         <v>23</v>
@@ -6032,27 +6032,27 @@
         <v>42</v>
       </c>
       <c r="D55" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E55" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F55" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G55">
-        <v>476</v>
+        <v>182</v>
       </c>
       <c r="H55" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I55" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B56" t="s">
         <v>23</v>
@@ -6061,27 +6061,27 @@
         <v>42</v>
       </c>
       <c r="D56" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E56" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F56" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G56">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="H56" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I56" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B57" t="s">
         <v>23</v>
@@ -6090,27 +6090,27 @@
         <v>42</v>
       </c>
       <c r="D57" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E57" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F57" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G57">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="H57" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I57" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B58" t="s">
         <v>23</v>
@@ -6119,27 +6119,27 @@
         <v>42</v>
       </c>
       <c r="D58" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E58" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F58" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G58">
-        <v>300</v>
+        <v>531</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I58" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B59" t="s">
         <v>23</v>
@@ -6148,27 +6148,27 @@
         <v>42</v>
       </c>
       <c r="D59" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E59" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F59" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G59">
-        <v>184</v>
+        <v>543</v>
       </c>
       <c r="H59" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I59" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B60" t="s">
         <v>23</v>
@@ -6177,27 +6177,27 @@
         <v>42</v>
       </c>
       <c r="D60" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E60" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F60" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G60">
-        <v>220</v>
+        <v>491</v>
       </c>
       <c r="H60" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I60" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B61" t="s">
         <v>23</v>
@@ -6206,4691 +6206,4691 @@
         <v>42</v>
       </c>
       <c r="D61" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E61" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F61" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G61">
-        <v>297</v>
+        <v>457</v>
       </c>
       <c r="H61" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I61" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B62" t="s">
         <v>25</v>
       </c>
       <c r="C62" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D62" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E62" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F62" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G62">
-        <v>565</v>
+        <v>419</v>
       </c>
       <c r="H62" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I62" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B63" t="s">
         <v>25</v>
       </c>
       <c r="C63" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D63" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E63" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F63" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G63">
-        <v>559</v>
+        <v>648</v>
       </c>
       <c r="H63" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I63" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B64" t="s">
         <v>25</v>
       </c>
       <c r="C64" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D64" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E64" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F64" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G64">
-        <v>475</v>
+        <v>787</v>
       </c>
       <c r="H64" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I64" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B65" t="s">
         <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D65" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E65" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F65" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G65">
-        <v>615</v>
+        <v>634</v>
       </c>
       <c r="H65" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I65" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B66" t="s">
         <v>25</v>
       </c>
       <c r="C66" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D66" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E66" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F66" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G66">
-        <v>635</v>
+        <v>343</v>
       </c>
       <c r="H66" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I66" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B67" t="s">
         <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D67" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E67" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F67" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G67">
-        <v>496</v>
+        <v>665</v>
       </c>
       <c r="H67" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I67" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B68" t="s">
         <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D68" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E68" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F68" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G68">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="H68" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I68" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B69" t="s">
         <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D69" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E69" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F69" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G69">
-        <v>260</v>
+        <v>496</v>
       </c>
       <c r="H69" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I69" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B70" t="s">
         <v>25</v>
       </c>
       <c r="C70" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D70" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E70" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F70" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G70">
-        <v>607</v>
+        <v>346</v>
       </c>
       <c r="H70" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I70" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B71" t="s">
         <v>25</v>
       </c>
       <c r="C71" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D71" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E71" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F71" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G71">
-        <v>363</v>
+        <v>776</v>
       </c>
       <c r="H71" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I71" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B72" t="s">
         <v>25</v>
       </c>
       <c r="C72" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D72" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E72" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F72" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G72">
-        <v>250</v>
+        <v>432</v>
       </c>
       <c r="H72" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I72" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B73" t="s">
         <v>25</v>
       </c>
       <c r="C73" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E73" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F73" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G73">
-        <v>666</v>
+        <v>264</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I73" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B74" t="s">
         <v>25</v>
       </c>
       <c r="C74" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E74" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G74">
-        <v>417</v>
+        <v>370</v>
       </c>
       <c r="H74" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I74" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B75" t="s">
         <v>25</v>
       </c>
       <c r="C75" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F75" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G75">
-        <v>295</v>
+        <v>502</v>
       </c>
       <c r="H75" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I75" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B76" t="s">
         <v>25</v>
       </c>
       <c r="C76" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D76" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E76" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F76" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G76">
-        <v>299</v>
+        <v>606</v>
       </c>
       <c r="H76" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I76" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B77" t="s">
         <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D77" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E77" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F77" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G77">
-        <v>312</v>
+        <v>653</v>
       </c>
       <c r="H77" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I77" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B78" t="s">
         <v>25</v>
       </c>
       <c r="C78" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D78" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E78" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F78" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G78">
-        <v>607</v>
+        <v>300</v>
       </c>
       <c r="H78" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I78" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B79" t="s">
         <v>25</v>
       </c>
       <c r="C79" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D79" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E79" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F79" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G79">
-        <v>617</v>
+        <v>595</v>
       </c>
       <c r="H79" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I79" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B80" t="s">
         <v>25</v>
       </c>
       <c r="C80" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D80" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E80" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F80" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G80">
-        <v>423</v>
+        <v>632</v>
       </c>
       <c r="H80" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I80" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B81" t="s">
         <v>25</v>
       </c>
       <c r="C81" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D81" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E81" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F81" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G81">
-        <v>562</v>
+        <v>614</v>
       </c>
       <c r="H81" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I81" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B82" t="s">
         <v>25</v>
       </c>
       <c r="C82" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D82" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E82" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F82" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G82">
-        <v>602</v>
+        <v>678</v>
       </c>
       <c r="H82" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I82" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B83" t="s">
         <v>25</v>
       </c>
       <c r="C83" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D83" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E83" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F83" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G83">
-        <v>771</v>
+        <v>482</v>
       </c>
       <c r="H83" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I83" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B84" t="s">
         <v>25</v>
       </c>
       <c r="C84" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D84" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E84" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F84" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G84">
-        <v>255</v>
+        <v>540</v>
       </c>
       <c r="H84" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I84" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B85" t="s">
         <v>25</v>
       </c>
       <c r="C85" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D85" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E85" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F85" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G85">
-        <v>411</v>
+        <v>552</v>
       </c>
       <c r="H85" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I85" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B86" t="s">
         <v>25</v>
       </c>
       <c r="C86" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D86" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E86" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F86" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G86">
-        <v>519</v>
+        <v>398</v>
       </c>
       <c r="H86" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I86" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B87" t="s">
         <v>25</v>
       </c>
       <c r="C87" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D87" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E87" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F87" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G87">
-        <v>254</v>
+        <v>633</v>
       </c>
       <c r="H87" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I87" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B88" t="s">
         <v>25</v>
       </c>
       <c r="C88" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D88" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E88" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F88" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G88">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H88" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I88" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B89" t="s">
         <v>25</v>
       </c>
       <c r="C89" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D89" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E89" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F89" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G89">
-        <v>652</v>
+        <v>712</v>
       </c>
       <c r="H89" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I89" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B90" t="s">
         <v>25</v>
       </c>
       <c r="C90" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D90" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E90" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F90" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G90">
-        <v>375</v>
+        <v>458</v>
       </c>
       <c r="H90" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I90" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B91" t="s">
         <v>25</v>
       </c>
       <c r="C91" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D91" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E91" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F91" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G91">
-        <v>519</v>
+        <v>398</v>
       </c>
       <c r="H91" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I91" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B92" t="s">
         <v>25</v>
       </c>
       <c r="C92" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D92" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E92" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F92" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G92">
-        <v>421</v>
+        <v>633</v>
       </c>
       <c r="H92" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I92" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B93" t="s">
         <v>25</v>
       </c>
       <c r="C93" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D93" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E93" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F93" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G93">
-        <v>553</v>
+        <v>768</v>
       </c>
       <c r="H93" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I93" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B94" t="s">
         <v>25</v>
       </c>
       <c r="C94" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D94" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E94" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F94" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G94">
-        <v>632</v>
+        <v>420</v>
       </c>
       <c r="H94" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I94" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B95" t="s">
         <v>25</v>
       </c>
       <c r="C95" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D95" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E95" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F95" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G95">
-        <v>676</v>
+        <v>772</v>
       </c>
       <c r="H95" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I95" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B96" t="s">
         <v>25</v>
       </c>
       <c r="C96" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D96" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E96" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F96" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G96">
-        <v>717</v>
+        <v>283</v>
       </c>
       <c r="H96" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I96" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B97" t="s">
         <v>25</v>
       </c>
       <c r="C97" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D97" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E97" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F97" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G97">
-        <v>360</v>
+        <v>555</v>
       </c>
       <c r="H97" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I97" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B98" t="s">
         <v>25</v>
       </c>
       <c r="C98" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D98" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E98" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F98" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G98">
-        <v>746</v>
+        <v>545</v>
       </c>
       <c r="H98" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I98" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B99" t="s">
         <v>25</v>
       </c>
       <c r="C99" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D99" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E99" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F99" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G99">
-        <v>575</v>
+        <v>482</v>
       </c>
       <c r="H99" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I99" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B100" t="s">
         <v>25</v>
       </c>
       <c r="C100" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D100" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E100" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F100" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G100">
-        <v>526</v>
+        <v>468</v>
       </c>
       <c r="H100" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I100" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B101" t="s">
         <v>25</v>
       </c>
       <c r="C101" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D101" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E101" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F101" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G101">
-        <v>280</v>
+        <v>583</v>
       </c>
       <c r="H101" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I101" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B102" t="s">
         <v>25</v>
       </c>
       <c r="C102" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D102" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E102" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F102" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G102">
-        <v>728</v>
+        <v>278</v>
       </c>
       <c r="H102" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I102" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B103" t="s">
         <v>25</v>
       </c>
       <c r="C103" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D103" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E103" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F103" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G103">
-        <v>436</v>
+        <v>785</v>
       </c>
       <c r="H103" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I103" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B104" t="s">
         <v>25</v>
       </c>
       <c r="C104" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D104" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E104" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F104" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G104">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="H104" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I104" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B105" t="s">
         <v>25</v>
       </c>
       <c r="C105" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D105" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E105" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F105" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G105">
-        <v>799</v>
+        <v>404</v>
       </c>
       <c r="H105" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I105" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B106" t="s">
         <v>25</v>
       </c>
       <c r="C106" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D106" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E106" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F106" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G106">
-        <v>541</v>
+        <v>493</v>
       </c>
       <c r="H106" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I106" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B107" t="s">
         <v>25</v>
       </c>
       <c r="C107" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D107" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E107" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F107" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G107">
-        <v>694</v>
+        <v>448</v>
       </c>
       <c r="H107" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I107" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B108" t="s">
         <v>25</v>
       </c>
       <c r="C108" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D108" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E108" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F108" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G108">
-        <v>790</v>
+        <v>439</v>
       </c>
       <c r="H108" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I108" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B109" t="s">
         <v>25</v>
       </c>
       <c r="C109" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D109" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E109" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F109" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G109">
-        <v>774</v>
+        <v>510</v>
       </c>
       <c r="H109" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I109" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B110" t="s">
         <v>25</v>
       </c>
       <c r="C110" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D110" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E110" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F110" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G110">
-        <v>534</v>
+        <v>726</v>
       </c>
       <c r="H110" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I110" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B111" t="s">
         <v>25</v>
       </c>
       <c r="C111" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D111" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E111" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F111" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G111">
-        <v>716</v>
+        <v>664</v>
       </c>
       <c r="H111" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I111" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B112" t="s">
         <v>25</v>
       </c>
       <c r="C112" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D112" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E112" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F112" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G112">
-        <v>523</v>
+        <v>731</v>
       </c>
       <c r="H112" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I112" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B113" t="s">
         <v>25</v>
       </c>
       <c r="C113" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D113" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E113" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F113" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G113">
-        <v>707</v>
+        <v>353</v>
       </c>
       <c r="H113" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I113" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B114" t="s">
         <v>25</v>
       </c>
       <c r="C114" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D114" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E114" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F114" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G114">
-        <v>569</v>
+        <v>709</v>
       </c>
       <c r="H114" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I114" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B115" t="s">
         <v>25</v>
       </c>
       <c r="C115" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D115" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E115" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F115" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G115">
-        <v>259</v>
+        <v>304</v>
       </c>
       <c r="H115" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I115" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B116" t="s">
         <v>25</v>
       </c>
       <c r="C116" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D116" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E116" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F116" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G116">
-        <v>637</v>
+        <v>566</v>
       </c>
       <c r="H116" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I116" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B117" t="s">
         <v>25</v>
       </c>
       <c r="C117" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D117" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E117" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F117" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G117">
-        <v>683</v>
+        <v>574</v>
       </c>
       <c r="H117" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I117" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B118" t="s">
         <v>25</v>
       </c>
       <c r="C118" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D118" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E118" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F118" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G118">
-        <v>490</v>
+        <v>394</v>
       </c>
       <c r="H118" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I118" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B119" t="s">
         <v>25</v>
       </c>
       <c r="C119" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D119" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E119" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F119" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G119">
-        <v>638</v>
+        <v>296</v>
       </c>
       <c r="H119" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I119" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B120" t="s">
         <v>25</v>
       </c>
       <c r="C120" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D120" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E120" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F120" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G120">
-        <v>743</v>
+        <v>616</v>
       </c>
       <c r="H120" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I120" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B121" t="s">
         <v>25</v>
       </c>
       <c r="C121" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D121" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E121" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F121" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G121">
-        <v>345</v>
+        <v>736</v>
       </c>
       <c r="H121" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I121" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B122" t="s">
         <v>25</v>
       </c>
       <c r="C122" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D122" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E122" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F122" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G122">
-        <v>522</v>
+        <v>575</v>
       </c>
       <c r="H122" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I122" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B123" t="s">
         <v>25</v>
       </c>
       <c r="C123" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D123" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E123" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F123" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G123">
-        <v>340</v>
+        <v>723</v>
       </c>
       <c r="H123" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I123" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B124" t="s">
         <v>25</v>
       </c>
       <c r="C124" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D124" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E124" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F124" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G124">
-        <v>652</v>
+        <v>549</v>
       </c>
       <c r="H124" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I124" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B125" t="s">
         <v>25</v>
       </c>
       <c r="C125" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D125" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E125" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F125" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="G125">
-        <v>576</v>
+        <v>477</v>
       </c>
       <c r="H125" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I125" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B126" t="s">
         <v>25</v>
       </c>
       <c r="C126" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D126" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E126" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F126" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G126">
-        <v>404</v>
+        <v>744</v>
       </c>
       <c r="H126" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I126" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B127" t="s">
         <v>25</v>
       </c>
       <c r="C127" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D127" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E127" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F127" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G127">
-        <v>441</v>
+        <v>607</v>
       </c>
       <c r="H127" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I127" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B128" t="s">
         <v>25</v>
       </c>
       <c r="C128" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D128" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E128" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F128" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="G128">
-        <v>541</v>
+        <v>456</v>
       </c>
       <c r="H128" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I128" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B129" t="s">
         <v>25</v>
       </c>
       <c r="C129" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D129" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E129" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F129" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="G129">
-        <v>366</v>
+        <v>771</v>
       </c>
       <c r="H129" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I129" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B130" t="s">
         <v>25</v>
       </c>
       <c r="C130" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D130" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E130" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F130" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G130">
-        <v>755</v>
+        <v>429</v>
       </c>
       <c r="H130" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I130" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B131" t="s">
         <v>25</v>
       </c>
       <c r="C131" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D131" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E131" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F131" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G131">
-        <v>782</v>
+        <v>603</v>
       </c>
       <c r="H131" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I131" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B132" t="s">
         <v>25</v>
       </c>
       <c r="C132" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D132" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E132" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F132" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G132">
-        <v>718</v>
+        <v>384</v>
       </c>
       <c r="H132" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I132" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B133" t="s">
         <v>25</v>
       </c>
       <c r="C133" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D133" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E133" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F133" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G133">
-        <v>770</v>
+        <v>301</v>
       </c>
       <c r="H133" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I133" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B134" t="s">
         <v>25</v>
       </c>
       <c r="C134" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D134" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E134" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F134" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G134">
-        <v>469</v>
+        <v>603</v>
       </c>
       <c r="H134" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I134" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B135" t="s">
         <v>25</v>
       </c>
       <c r="C135" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D135" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E135" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F135" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G135">
-        <v>446</v>
+        <v>333</v>
       </c>
       <c r="H135" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I135" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B136" t="s">
         <v>25</v>
       </c>
       <c r="C136" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D136" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E136" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F136" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G136">
-        <v>784</v>
+        <v>714</v>
       </c>
       <c r="H136" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I136" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B137" t="s">
         <v>25</v>
       </c>
       <c r="C137" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D137" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E137" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F137" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G137">
-        <v>719</v>
+        <v>288</v>
       </c>
       <c r="H137" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I137" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B138" t="s">
         <v>25</v>
       </c>
       <c r="C138" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D138" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E138" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F138" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G138">
-        <v>602</v>
+        <v>674</v>
       </c>
       <c r="H138" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I138" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B139" t="s">
         <v>25</v>
       </c>
       <c r="C139" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D139" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E139" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F139" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G139">
-        <v>796</v>
+        <v>662</v>
       </c>
       <c r="H139" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I139" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B140" t="s">
         <v>25</v>
       </c>
       <c r="C140" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D140" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E140" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F140" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G140">
-        <v>448</v>
+        <v>714</v>
       </c>
       <c r="H140" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I140" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B141" t="s">
         <v>25</v>
       </c>
       <c r="C141" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D141" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E141" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F141" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G141">
-        <v>308</v>
+        <v>266</v>
       </c>
       <c r="H141" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I141" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B142" t="s">
         <v>25</v>
       </c>
       <c r="C142" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D142" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E142" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F142" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G142">
-        <v>307</v>
+        <v>687</v>
       </c>
       <c r="H142" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I142" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B143" t="s">
         <v>25</v>
       </c>
       <c r="C143" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D143" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E143" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F143" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G143">
-        <v>511</v>
+        <v>535</v>
       </c>
       <c r="H143" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I143" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B144" t="s">
         <v>25</v>
       </c>
       <c r="C144" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D144" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E144" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F144" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G144">
-        <v>300</v>
+        <v>727</v>
       </c>
       <c r="H144" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I144" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B145" t="s">
         <v>25</v>
       </c>
       <c r="C145" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D145" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E145" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F145" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G145">
-        <v>770</v>
+        <v>486</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I145" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B146" t="s">
         <v>25</v>
       </c>
       <c r="C146" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D146" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E146" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F146" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G146">
-        <v>279</v>
+        <v>765</v>
       </c>
       <c r="H146" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I146" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B147" t="s">
         <v>25</v>
       </c>
       <c r="C147" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D147" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E147" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F147" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G147">
-        <v>358</v>
+        <v>795</v>
       </c>
       <c r="H147" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I147" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B148" t="s">
         <v>25</v>
       </c>
       <c r="C148" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D148" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E148" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F148" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G148">
-        <v>331</v>
+        <v>717</v>
       </c>
       <c r="H148" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I148" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B149" t="s">
         <v>25</v>
       </c>
       <c r="C149" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D149" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E149" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F149" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G149">
-        <v>400</v>
+        <v>348</v>
       </c>
       <c r="H149" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I149" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B150" t="s">
         <v>25</v>
       </c>
       <c r="C150" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D150" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E150" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F150" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G150">
-        <v>534</v>
+        <v>583</v>
       </c>
       <c r="H150" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I150" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B151" t="s">
         <v>25</v>
       </c>
       <c r="C151" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D151" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E151" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F151" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="G151">
-        <v>272</v>
+        <v>415</v>
       </c>
       <c r="H151" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I151" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B152" t="s">
         <v>25</v>
       </c>
       <c r="C152" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D152" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="E152" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F152" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="G152">
-        <v>632</v>
+        <v>360</v>
       </c>
       <c r="H152" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I152" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B153" t="s">
         <v>25</v>
       </c>
       <c r="C153" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D153" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E153" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F153" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G153">
-        <v>710</v>
+        <v>488</v>
       </c>
       <c r="H153" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I153" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B154" t="s">
         <v>25</v>
       </c>
       <c r="C154" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D154" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E154" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F154" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G154">
-        <v>530</v>
+        <v>776</v>
       </c>
       <c r="H154" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I154" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B155" t="s">
         <v>25</v>
       </c>
       <c r="C155" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D155" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E155" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F155" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G155">
-        <v>478</v>
+        <v>548</v>
       </c>
       <c r="H155" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I155" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B156" t="s">
         <v>25</v>
       </c>
       <c r="C156" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D156" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E156" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F156" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G156">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="H156" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I156" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B157" t="s">
         <v>25</v>
       </c>
       <c r="C157" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D157" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E157" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F157" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G157">
-        <v>286</v>
+        <v>591</v>
       </c>
       <c r="H157" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I157" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B158" t="s">
         <v>25</v>
       </c>
       <c r="C158" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D158" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E158" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F158" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="G158">
-        <v>797</v>
+        <v>594</v>
       </c>
       <c r="H158" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I158" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B159" t="s">
         <v>25</v>
       </c>
       <c r="C159" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D159" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E159" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F159" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G159">
-        <v>694</v>
+        <v>592</v>
       </c>
       <c r="H159" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I159" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B160" t="s">
         <v>25</v>
       </c>
       <c r="C160" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D160" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E160" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F160" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="G160">
-        <v>664</v>
+        <v>315</v>
       </c>
       <c r="H160" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I160" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B161" t="s">
         <v>25</v>
       </c>
       <c r="C161" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D161" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E161" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F161" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="G161">
-        <v>697</v>
+        <v>427</v>
       </c>
       <c r="H161" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I161" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B162" t="s">
         <v>27</v>
       </c>
       <c r="C162" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D162" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E162" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F162" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="G162">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="H162" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I162" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B163" t="s">
         <v>27</v>
       </c>
       <c r="C163" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D163" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E163" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F163" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G163">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="H163" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I163" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B164" t="s">
         <v>27</v>
       </c>
       <c r="C164" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D164" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="E164" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F164" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="G164">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H164" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I164" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B165" t="s">
         <v>27</v>
       </c>
       <c r="C165" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D165" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="E165" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F165" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G165">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="H165" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I165" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B166" t="s">
         <v>27</v>
       </c>
       <c r="C166" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D166" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E166" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F166" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G166">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="H166" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I166" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B167" t="s">
         <v>27</v>
       </c>
       <c r="C167" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D167" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E167" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F167" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="G167">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="H167" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I167" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B168" t="s">
         <v>27</v>
       </c>
       <c r="C168" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D168" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E168" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F168" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G168">
-        <v>190</v>
+        <v>156</v>
       </c>
       <c r="H168" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I168" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B169" t="s">
         <v>27</v>
       </c>
       <c r="C169" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D169" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E169" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F169" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="G169">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H169" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I169" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B170" t="s">
         <v>27</v>
       </c>
       <c r="C170" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D170" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E170" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F170" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G170">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H170" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I170" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B171" t="s">
         <v>27</v>
       </c>
       <c r="C171" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D171" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E171" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F171" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="G171">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="H171" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I171" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B172" t="s">
         <v>27</v>
       </c>
       <c r="C172" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D172" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E172" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F172" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="G172">
-        <v>242</v>
+        <v>207</v>
       </c>
       <c r="H172" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I172" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B173" t="s">
         <v>27</v>
       </c>
       <c r="C173" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D173" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E173" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F173" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G173">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="H173" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I173" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B174" t="s">
         <v>27</v>
       </c>
       <c r="C174" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D174" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E174" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F174" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="G174">
-        <v>135</v>
+        <v>217</v>
       </c>
       <c r="H174" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I174" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B175" t="s">
         <v>27</v>
       </c>
       <c r="C175" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D175" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E175" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F175" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="G175">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="H175" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I175" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B176" t="s">
         <v>27</v>
       </c>
       <c r="C176" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D176" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E176" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F176" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G176">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="H176" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I176" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B177" t="s">
         <v>27</v>
       </c>
       <c r="C177" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D177" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E177" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="F177" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="G177">
-        <v>166</v>
+        <v>212</v>
       </c>
       <c r="H177" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I177" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B178" t="s">
         <v>27</v>
       </c>
       <c r="C178" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D178" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E178" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F178" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="G178">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H178" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I178" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B179" t="s">
         <v>27</v>
       </c>
       <c r="C179" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D179" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E179" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F179" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="G179">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="H179" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I179" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B180" t="s">
         <v>27</v>
       </c>
       <c r="C180" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D180" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E180" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F180" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="G180">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="H180" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I180" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B181" t="s">
         <v>27</v>
       </c>
       <c r="C181" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D181" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E181" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F181" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G181">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="H181" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I181" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B182" t="s">
         <v>27</v>
       </c>
       <c r="C182" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D182" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E182" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="F182" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="G182">
-        <v>100</v>
+        <v>247</v>
       </c>
       <c r="H182" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I182" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B183" t="s">
         <v>27</v>
       </c>
       <c r="C183" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D183" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E183" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="F183" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G183">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="H183" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I183" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B184" t="s">
         <v>27</v>
       </c>
       <c r="C184" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D184" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E184" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F184" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="G184">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="H184" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I184" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B185" t="s">
         <v>27</v>
       </c>
       <c r="C185" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D185" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E185" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F185" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G185">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="H185" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I185" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B186" t="s">
         <v>27</v>
       </c>
       <c r="C186" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D186" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E186" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F186" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G186">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="H186" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I186" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B187" t="s">
         <v>27</v>
       </c>
       <c r="C187" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D187" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E187" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F187" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="G187">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="H187" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I187" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B188" t="s">
         <v>27</v>
       </c>
       <c r="C188" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D188" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="E188" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="F188" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="G188">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H188" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I188" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B189" t="s">
         <v>27</v>
       </c>
       <c r="C189" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D189" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E189" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F189" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G189">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="H189" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I189" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B190" t="s">
         <v>27</v>
       </c>
       <c r="C190" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D190" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E190" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F190" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G190">
-        <v>195</v>
+        <v>65</v>
       </c>
       <c r="H190" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I190" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B191" t="s">
         <v>27</v>
       </c>
       <c r="C191" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D191" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E191" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F191" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G191">
-        <v>213</v>
+        <v>98</v>
       </c>
       <c r="H191" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I191" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B192" t="s">
         <v>27</v>
       </c>
       <c r="C192" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D192" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E192" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F192" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G192">
-        <v>66</v>
+        <v>223</v>
       </c>
       <c r="H192" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I192" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B193" t="s">
         <v>27</v>
       </c>
       <c r="C193" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D193" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E193" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F193" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="G193">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="H193" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I193" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B194" t="s">
         <v>27</v>
       </c>
       <c r="C194" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D194" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E194" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F194" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="G194">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="H194" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I194" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B195" t="s">
         <v>27</v>
       </c>
       <c r="C195" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D195" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E195" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F195" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="G195">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="H195" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I195" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B196" t="s">
         <v>27</v>
       </c>
       <c r="C196" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D196" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E196" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F196" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G196">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="H196" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I196" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B197" t="s">
         <v>27</v>
       </c>
       <c r="C197" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D197" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E197" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F197" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="G197">
-        <v>193</v>
+        <v>127</v>
       </c>
       <c r="H197" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I197" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B198" t="s">
         <v>27</v>
       </c>
       <c r="C198" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D198" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="E198" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="F198" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="G198">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="H198" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I198" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B199" t="s">
         <v>27</v>
       </c>
       <c r="C199" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D199" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E199" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F199" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G199">
-        <v>162</v>
+        <v>95</v>
       </c>
       <c r="H199" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I199" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B200" t="s">
         <v>27</v>
       </c>
       <c r="C200" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D200" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E200" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F200" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G200">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="H200" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I200" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B201" t="s">
         <v>27</v>
       </c>
       <c r="C201" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D201" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E201" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F201" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G201">
-        <v>243</v>
+        <v>163</v>
       </c>
       <c r="H201" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I201" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B202" t="s">
         <v>27</v>
       </c>
       <c r="C202" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D202" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E202" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F202" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="G202">
-        <v>186</v>
+        <v>129</v>
       </c>
       <c r="H202" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I202" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B203" t="s">
         <v>27</v>
       </c>
       <c r="C203" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D203" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E203" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F203" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G203">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="H203" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I203" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B204" t="s">
         <v>27</v>
       </c>
       <c r="C204" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D204" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E204" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F204" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="G204">
-        <v>155</v>
+        <v>225</v>
       </c>
       <c r="H204" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I204" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B205" t="s">
         <v>27</v>
       </c>
       <c r="C205" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D205" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E205" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="F205" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G205">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="H205" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I205" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B206" t="s">
         <v>27</v>
       </c>
       <c r="C206" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D206" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E206" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F206" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="G206">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="H206" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I206" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B207" t="s">
         <v>27</v>
       </c>
       <c r="C207" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D207" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E207" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="F207" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="G207">
-        <v>189</v>
+        <v>123</v>
       </c>
       <c r="H207" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I207" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B208" t="s">
         <v>27</v>
       </c>
       <c r="C208" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D208" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E208" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F208" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="G208">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H208" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I208" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B209" t="s">
         <v>27</v>
       </c>
       <c r="C209" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D209" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="E209" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="F209" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="G209">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="H209" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I209" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B210" t="s">
         <v>27</v>
       </c>
       <c r="C210" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D210" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E210" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="F210" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="G210">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="H210" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I210" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B211" t="s">
         <v>27</v>
       </c>
       <c r="C211" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D211" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E211" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="F211" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G211">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="H211" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I211" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B212" t="s">
         <v>27</v>
       </c>
       <c r="C212" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D212" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E212" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F212" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="G212">
-        <v>177</v>
+        <v>114</v>
       </c>
       <c r="H212" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I212" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B213" t="s">
         <v>27</v>
       </c>
       <c r="C213" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D213" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E213" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="F213" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="G213">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="H213" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I213" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B214" t="s">
         <v>27</v>
       </c>
       <c r="C214" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D214" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E214" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F214" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="G214">
-        <v>186</v>
+        <v>92</v>
       </c>
       <c r="H214" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I214" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B215" t="s">
         <v>27</v>
       </c>
       <c r="C215" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D215" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E215" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="F215" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="G215">
-        <v>140</v>
+        <v>246</v>
       </c>
       <c r="H215" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I215" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B216" t="s">
         <v>27</v>
       </c>
       <c r="C216" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D216" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E216" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F216" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="G216">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="H216" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I216" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B217" t="s">
         <v>27</v>
       </c>
       <c r="C217" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D217" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="E217" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F217" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="G217">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H217" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I217" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B218" t="s">
         <v>27</v>
       </c>
       <c r="C218" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D218" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="E218" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="F218" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="G218">
-        <v>247</v>
+        <v>176</v>
       </c>
       <c r="H218" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I218" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B219" t="s">
         <v>27</v>
       </c>
       <c r="C219" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D219" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="E219" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F219" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="G219">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="H219" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I219" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B220" t="s">
         <v>27</v>
       </c>
       <c r="C220" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D220" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E220" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F220" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G220">
-        <v>175</v>
+        <v>246</v>
       </c>
       <c r="H220" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I220" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B221" t="s">
         <v>27</v>
       </c>
       <c r="C221" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D221" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="E221" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="F221" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="G221">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H221" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I221" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B222" t="s">
         <v>29</v>
       </c>
       <c r="C222" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D222" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="E222" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F222" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="G222">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="H222" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I222" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
@@ -10901,7 +10901,7 @@
         <v>29</v>
       </c>
       <c r="C223" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D223" t="s">
         <v>933</v>
@@ -10913,13 +10913,13 @@
         <v>935</v>
       </c>
       <c r="G223">
-        <v>478</v>
+        <v>394</v>
       </c>
       <c r="H223" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I223" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
@@ -10930,7 +10930,7 @@
         <v>29</v>
       </c>
       <c r="C224" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D224" t="s">
         <v>937</v>
@@ -10942,13 +10942,13 @@
         <v>939</v>
       </c>
       <c r="G224">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="H224" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I224" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
@@ -10959,7 +10959,7 @@
         <v>29</v>
       </c>
       <c r="C225" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D225" t="s">
         <v>941</v>
@@ -10971,13 +10971,13 @@
         <v>943</v>
       </c>
       <c r="G225">
-        <v>355</v>
+        <v>506</v>
       </c>
       <c r="H225" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I225" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
@@ -10988,7 +10988,7 @@
         <v>29</v>
       </c>
       <c r="C226" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D226" t="s">
         <v>945</v>
@@ -11000,13 +11000,13 @@
         <v>947</v>
       </c>
       <c r="G226">
-        <v>350</v>
+        <v>218</v>
       </c>
       <c r="H226" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I226" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
@@ -11017,7 +11017,7 @@
         <v>29</v>
       </c>
       <c r="C227" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D227" t="s">
         <v>949</v>
@@ -11029,13 +11029,13 @@
         <v>951</v>
       </c>
       <c r="G227">
-        <v>454</v>
+        <v>369</v>
       </c>
       <c r="H227" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I227" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
@@ -11046,7 +11046,7 @@
         <v>29</v>
       </c>
       <c r="C228" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D228" t="s">
         <v>953</v>
@@ -11058,13 +11058,13 @@
         <v>955</v>
       </c>
       <c r="G228">
-        <v>206</v>
+        <v>496</v>
       </c>
       <c r="H228" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I228" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
@@ -11075,7 +11075,7 @@
         <v>29</v>
       </c>
       <c r="C229" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D229" t="s">
         <v>957</v>
@@ -11087,13 +11087,13 @@
         <v>959</v>
       </c>
       <c r="G229">
-        <v>447</v>
+        <v>264</v>
       </c>
       <c r="H229" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I229" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
@@ -11104,7 +11104,7 @@
         <v>29</v>
       </c>
       <c r="C230" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D230" t="s">
         <v>961</v>
@@ -11116,13 +11116,13 @@
         <v>963</v>
       </c>
       <c r="G230">
-        <v>327</v>
+        <v>271</v>
       </c>
       <c r="H230" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I230" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
@@ -11133,7 +11133,7 @@
         <v>29</v>
       </c>
       <c r="C231" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D231" t="s">
         <v>965</v>
@@ -11145,13 +11145,13 @@
         <v>967</v>
       </c>
       <c r="G231">
-        <v>413</v>
+        <v>286</v>
       </c>
       <c r="H231" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I231" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
@@ -11162,7 +11162,7 @@
         <v>29</v>
       </c>
       <c r="C232" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D232" t="s">
         <v>969</v>
@@ -11174,13 +11174,13 @@
         <v>971</v>
       </c>
       <c r="G232">
-        <v>360</v>
+        <v>572</v>
       </c>
       <c r="H232" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I232" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
@@ -11191,7 +11191,7 @@
         <v>29</v>
       </c>
       <c r="C233" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D233" t="s">
         <v>973</v>
@@ -11203,13 +11203,13 @@
         <v>975</v>
       </c>
       <c r="G233">
-        <v>323</v>
+        <v>370</v>
       </c>
       <c r="H233" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I233" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
@@ -11220,7 +11220,7 @@
         <v>29</v>
       </c>
       <c r="C234" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D234" t="s">
         <v>977</v>
@@ -11232,13 +11232,13 @@
         <v>979</v>
       </c>
       <c r="G234">
-        <v>524</v>
+        <v>351</v>
       </c>
       <c r="H234" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I234" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
@@ -11249,7 +11249,7 @@
         <v>29</v>
       </c>
       <c r="C235" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D235" t="s">
         <v>981</v>
@@ -11261,13 +11261,13 @@
         <v>983</v>
       </c>
       <c r="G235">
-        <v>425</v>
+        <v>540</v>
       </c>
       <c r="H235" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I235" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
@@ -11278,7 +11278,7 @@
         <v>29</v>
       </c>
       <c r="C236" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D236" t="s">
         <v>985</v>
@@ -11290,13 +11290,13 @@
         <v>987</v>
       </c>
       <c r="G236">
-        <v>398</v>
+        <v>221</v>
       </c>
       <c r="H236" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I236" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
@@ -11307,7 +11307,7 @@
         <v>29</v>
       </c>
       <c r="C237" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D237" t="s">
         <v>989</v>
@@ -11319,13 +11319,13 @@
         <v>991</v>
       </c>
       <c r="G237">
-        <v>546</v>
+        <v>595</v>
       </c>
       <c r="H237" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I237" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
@@ -11336,7 +11336,7 @@
         <v>29</v>
       </c>
       <c r="C238" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D238" t="s">
         <v>993</v>
@@ -11348,13 +11348,13 @@
         <v>995</v>
       </c>
       <c r="G238">
-        <v>451</v>
+        <v>577</v>
       </c>
       <c r="H238" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I238" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
@@ -11365,7 +11365,7 @@
         <v>29</v>
       </c>
       <c r="C239" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D239" t="s">
         <v>997</v>
@@ -11377,13 +11377,13 @@
         <v>999</v>
       </c>
       <c r="G239">
-        <v>441</v>
+        <v>216</v>
       </c>
       <c r="H239" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I239" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
@@ -11394,7 +11394,7 @@
         <v>29</v>
       </c>
       <c r="C240" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D240" t="s">
         <v>1001</v>
@@ -11406,13 +11406,13 @@
         <v>1003</v>
       </c>
       <c r="G240">
-        <v>296</v>
+        <v>219</v>
       </c>
       <c r="H240" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I240" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
@@ -11423,7 +11423,7 @@
         <v>29</v>
       </c>
       <c r="C241" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D241" t="s">
         <v>1005</v>
@@ -11435,13 +11435,13 @@
         <v>1007</v>
       </c>
       <c r="G241">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="H241" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I241" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
@@ -11452,7 +11452,7 @@
         <v>29</v>
       </c>
       <c r="C242" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D242" t="s">
         <v>1009</v>
@@ -11464,13 +11464,13 @@
         <v>1011</v>
       </c>
       <c r="G242">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="H242" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I242" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
@@ -11481,7 +11481,7 @@
         <v>29</v>
       </c>
       <c r="C243" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D243" t="s">
         <v>1013</v>
@@ -11493,13 +11493,13 @@
         <v>1015</v>
       </c>
       <c r="G243">
-        <v>408</v>
+        <v>341</v>
       </c>
       <c r="H243" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I243" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
@@ -11510,7 +11510,7 @@
         <v>29</v>
       </c>
       <c r="C244" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D244" t="s">
         <v>1017</v>
@@ -11522,13 +11522,13 @@
         <v>1019</v>
       </c>
       <c r="G244">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="H244" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I244" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
@@ -11539,7 +11539,7 @@
         <v>29</v>
       </c>
       <c r="C245" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D245" t="s">
         <v>1021</v>
@@ -11551,13 +11551,13 @@
         <v>1023</v>
       </c>
       <c r="G245">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="H245" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I245" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
@@ -11568,7 +11568,7 @@
         <v>29</v>
       </c>
       <c r="C246" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D246" t="s">
         <v>1025</v>
@@ -11580,13 +11580,13 @@
         <v>1027</v>
       </c>
       <c r="G246">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="H246" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I246" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
@@ -11597,7 +11597,7 @@
         <v>29</v>
       </c>
       <c r="C247" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D247" t="s">
         <v>1029</v>
@@ -11609,13 +11609,13 @@
         <v>1031</v>
       </c>
       <c r="G247">
-        <v>391</v>
+        <v>591</v>
       </c>
       <c r="H247" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I247" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
@@ -11626,7 +11626,7 @@
         <v>29</v>
       </c>
       <c r="C248" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D248" t="s">
         <v>1033</v>
@@ -11638,13 +11638,13 @@
         <v>1035</v>
       </c>
       <c r="G248">
-        <v>308</v>
+        <v>502</v>
       </c>
       <c r="H248" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I248" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
@@ -11655,7 +11655,7 @@
         <v>29</v>
       </c>
       <c r="C249" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D249" t="s">
         <v>1037</v>
@@ -11667,13 +11667,13 @@
         <v>1039</v>
       </c>
       <c r="G249">
-        <v>457</v>
+        <v>424</v>
       </c>
       <c r="H249" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I249" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
@@ -11684,7 +11684,7 @@
         <v>29</v>
       </c>
       <c r="C250" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D250" t="s">
         <v>1041</v>
@@ -11696,13 +11696,13 @@
         <v>1043</v>
       </c>
       <c r="G250">
-        <v>514</v>
+        <v>429</v>
       </c>
       <c r="H250" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I250" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
@@ -11713,7 +11713,7 @@
         <v>29</v>
       </c>
       <c r="C251" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D251" t="s">
         <v>1045</v>
@@ -11725,13 +11725,13 @@
         <v>1047</v>
       </c>
       <c r="G251">
-        <v>309</v>
+        <v>482</v>
       </c>
       <c r="H251" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I251" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
@@ -11742,7 +11742,7 @@
         <v>29</v>
       </c>
       <c r="C252" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D252" t="s">
         <v>1049</v>
@@ -11754,13 +11754,13 @@
         <v>1051</v>
       </c>
       <c r="G252">
-        <v>394</v>
+        <v>299</v>
       </c>
       <c r="H252" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I252" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
@@ -11771,7 +11771,7 @@
         <v>29</v>
       </c>
       <c r="C253" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D253" t="s">
         <v>1053</v>
@@ -11783,13 +11783,13 @@
         <v>1055</v>
       </c>
       <c r="G253">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="H253" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I253" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
@@ -11800,7 +11800,7 @@
         <v>29</v>
       </c>
       <c r="C254" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D254" t="s">
         <v>1057</v>
@@ -11812,13 +11812,13 @@
         <v>1059</v>
       </c>
       <c r="G254">
-        <v>334</v>
+        <v>443</v>
       </c>
       <c r="H254" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I254" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
@@ -11829,7 +11829,7 @@
         <v>29</v>
       </c>
       <c r="C255" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D255" t="s">
         <v>1061</v>
@@ -11841,13 +11841,13 @@
         <v>1063</v>
       </c>
       <c r="G255">
-        <v>465</v>
+        <v>514</v>
       </c>
       <c r="H255" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I255" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
@@ -11858,7 +11858,7 @@
         <v>29</v>
       </c>
       <c r="C256" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D256" t="s">
         <v>1065</v>
@@ -11870,13 +11870,13 @@
         <v>1067</v>
       </c>
       <c r="G256">
-        <v>598</v>
+        <v>388</v>
       </c>
       <c r="H256" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I256" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
@@ -11887,7 +11887,7 @@
         <v>29</v>
       </c>
       <c r="C257" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D257" t="s">
         <v>1069</v>
@@ -11899,13 +11899,13 @@
         <v>1071</v>
       </c>
       <c r="G257">
-        <v>493</v>
+        <v>524</v>
       </c>
       <c r="H257" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I257" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
@@ -11916,7 +11916,7 @@
         <v>29</v>
       </c>
       <c r="C258" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D258" t="s">
         <v>1073</v>
@@ -11928,13 +11928,13 @@
         <v>1075</v>
       </c>
       <c r="G258">
-        <v>450</v>
+        <v>208</v>
       </c>
       <c r="H258" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I258" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
@@ -11945,7 +11945,7 @@
         <v>29</v>
       </c>
       <c r="C259" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D259" t="s">
         <v>1077</v>
@@ -11957,13 +11957,13 @@
         <v>1079</v>
       </c>
       <c r="G259">
-        <v>234</v>
+        <v>418</v>
       </c>
       <c r="H259" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I259" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
@@ -11974,7 +11974,7 @@
         <v>29</v>
       </c>
       <c r="C260" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D260" t="s">
         <v>1081</v>
@@ -11986,13 +11986,13 @@
         <v>1083</v>
       </c>
       <c r="G260">
-        <v>525</v>
+        <v>421</v>
       </c>
       <c r="H260" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I260" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
@@ -12003,7 +12003,7 @@
         <v>29</v>
       </c>
       <c r="C261" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D261" t="s">
         <v>1085</v>
@@ -12015,13 +12015,13 @@
         <v>1087</v>
       </c>
       <c r="G261">
-        <v>508</v>
+        <v>463</v>
       </c>
       <c r="H261" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I261" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
@@ -12032,7 +12032,7 @@
         <v>29</v>
       </c>
       <c r="C262" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D262" t="s">
         <v>1089</v>
@@ -12044,13 +12044,13 @@
         <v>1091</v>
       </c>
       <c r="G262">
-        <v>260</v>
+        <v>389</v>
       </c>
       <c r="H262" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I262" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
@@ -12061,7 +12061,7 @@
         <v>29</v>
       </c>
       <c r="C263" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D263" t="s">
         <v>1093</v>
@@ -12073,13 +12073,13 @@
         <v>1095</v>
       </c>
       <c r="G263">
-        <v>569</v>
+        <v>321</v>
       </c>
       <c r="H263" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I263" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
@@ -12090,7 +12090,7 @@
         <v>29</v>
       </c>
       <c r="C264" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D264" t="s">
         <v>1097</v>
@@ -12102,13 +12102,13 @@
         <v>1099</v>
       </c>
       <c r="G264">
-        <v>374</v>
+        <v>579</v>
       </c>
       <c r="H264" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I264" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
@@ -12119,7 +12119,7 @@
         <v>29</v>
       </c>
       <c r="C265" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D265" t="s">
         <v>1101</v>
@@ -12131,13 +12131,13 @@
         <v>1103</v>
       </c>
       <c r="G265">
-        <v>367</v>
+        <v>336</v>
       </c>
       <c r="H265" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I265" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
@@ -12148,7 +12148,7 @@
         <v>29</v>
       </c>
       <c r="C266" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D266" t="s">
         <v>1105</v>
@@ -12160,13 +12160,13 @@
         <v>1107</v>
       </c>
       <c r="G266">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="H266" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I266" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
@@ -12177,7 +12177,7 @@
         <v>29</v>
       </c>
       <c r="C267" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D267" t="s">
         <v>1109</v>
@@ -12189,13 +12189,13 @@
         <v>1111</v>
       </c>
       <c r="G267">
-        <v>243</v>
+        <v>458</v>
       </c>
       <c r="H267" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I267" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
@@ -12206,7 +12206,7 @@
         <v>29</v>
       </c>
       <c r="C268" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D268" t="s">
         <v>1113</v>
@@ -12218,13 +12218,13 @@
         <v>1115</v>
       </c>
       <c r="G268">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="H268" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I268" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
@@ -12235,7 +12235,7 @@
         <v>29</v>
       </c>
       <c r="C269" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D269" t="s">
         <v>1117</v>
@@ -12247,13 +12247,13 @@
         <v>1119</v>
       </c>
       <c r="G269">
-        <v>320</v>
+        <v>505</v>
       </c>
       <c r="H269" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I269" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
@@ -12264,7 +12264,7 @@
         <v>29</v>
       </c>
       <c r="C270" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D270" t="s">
         <v>1121</v>
@@ -12276,13 +12276,13 @@
         <v>1123</v>
       </c>
       <c r="G270">
-        <v>329</v>
+        <v>494</v>
       </c>
       <c r="H270" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I270" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
@@ -12293,7 +12293,7 @@
         <v>29</v>
       </c>
       <c r="C271" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D271" t="s">
         <v>1125</v>
@@ -12305,13 +12305,13 @@
         <v>1127</v>
       </c>
       <c r="G271">
-        <v>342</v>
+        <v>536</v>
       </c>
       <c r="H271" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I271" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
@@ -12334,13 +12334,13 @@
         <v>1132</v>
       </c>
       <c r="G272">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="H272" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I272" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
@@ -12363,13 +12363,13 @@
         <v>1136</v>
       </c>
       <c r="G273">
-        <v>273</v>
+        <v>100</v>
       </c>
       <c r="H273" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I273" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
@@ -12392,13 +12392,13 @@
         <v>1140</v>
       </c>
       <c r="G274">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="H274" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I274" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
@@ -12421,13 +12421,13 @@
         <v>1144</v>
       </c>
       <c r="G275">
-        <v>101</v>
+        <v>200</v>
       </c>
       <c r="H275" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I275" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
@@ -12450,13 +12450,13 @@
         <v>1148</v>
       </c>
       <c r="G276">
-        <v>280</v>
+        <v>142</v>
       </c>
       <c r="H276" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I276" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
@@ -12479,13 +12479,13 @@
         <v>1152</v>
       </c>
       <c r="G277">
-        <v>240</v>
+        <v>182</v>
       </c>
       <c r="H277" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I277" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
@@ -12508,13 +12508,13 @@
         <v>1156</v>
       </c>
       <c r="G278">
-        <v>103</v>
+        <v>288</v>
       </c>
       <c r="H278" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I278" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
@@ -12537,13 +12537,13 @@
         <v>1160</v>
       </c>
       <c r="G279">
-        <v>148</v>
+        <v>261</v>
       </c>
       <c r="H279" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I279" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
@@ -12566,13 +12566,13 @@
         <v>1164</v>
       </c>
       <c r="G280">
-        <v>234</v>
+        <v>152</v>
       </c>
       <c r="H280" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I280" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
@@ -12595,13 +12595,13 @@
         <v>1168</v>
       </c>
       <c r="G281">
-        <v>124</v>
+        <v>205</v>
       </c>
       <c r="H281" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I281" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
@@ -12624,13 +12624,13 @@
         <v>1172</v>
       </c>
       <c r="G282">
-        <v>231</v>
+        <v>189</v>
       </c>
       <c r="H282" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I282" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
@@ -12653,13 +12653,13 @@
         <v>1176</v>
       </c>
       <c r="G283">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="H283" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I283" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
@@ -12682,13 +12682,13 @@
         <v>1180</v>
       </c>
       <c r="G284">
-        <v>297</v>
+        <v>186</v>
       </c>
       <c r="H284" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I284" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
@@ -12711,13 +12711,13 @@
         <v>1184</v>
       </c>
       <c r="G285">
-        <v>274</v>
+        <v>222</v>
       </c>
       <c r="H285" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I285" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
@@ -12740,13 +12740,13 @@
         <v>1188</v>
       </c>
       <c r="G286">
-        <v>310</v>
+        <v>102</v>
       </c>
       <c r="H286" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I286" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
@@ -12769,13 +12769,13 @@
         <v>1192</v>
       </c>
       <c r="G287">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="H287" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I287" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
@@ -12798,13 +12798,13 @@
         <v>1196</v>
       </c>
       <c r="G288">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="H288" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I288" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.25">
@@ -12827,13 +12827,13 @@
         <v>1200</v>
       </c>
       <c r="G289">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H289" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I289" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
@@ -12856,13 +12856,13 @@
         <v>1204</v>
       </c>
       <c r="G290">
-        <v>163</v>
+        <v>289</v>
       </c>
       <c r="H290" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I290" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
@@ -12885,13 +12885,13 @@
         <v>1208</v>
       </c>
       <c r="G291">
-        <v>170</v>
+        <v>295</v>
       </c>
       <c r="H291" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I291" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.25">
@@ -12914,13 +12914,13 @@
         <v>1212</v>
       </c>
       <c r="G292">
-        <v>152</v>
+        <v>300</v>
       </c>
       <c r="H292" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I292" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
@@ -12943,13 +12943,13 @@
         <v>1216</v>
       </c>
       <c r="G293">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="H293" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I293" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
@@ -12972,13 +12972,13 @@
         <v>1220</v>
       </c>
       <c r="G294">
-        <v>327</v>
+        <v>272</v>
       </c>
       <c r="H294" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I294" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
@@ -13001,13 +13001,13 @@
         <v>1224</v>
       </c>
       <c r="G295">
-        <v>297</v>
+        <v>224</v>
       </c>
       <c r="H295" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I295" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
@@ -13030,13 +13030,13 @@
         <v>1228</v>
       </c>
       <c r="G296">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="H296" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I296" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
@@ -13059,13 +13059,13 @@
         <v>1232</v>
       </c>
       <c r="G297">
-        <v>103</v>
+        <v>191</v>
       </c>
       <c r="H297" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I297" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
@@ -13088,13 +13088,13 @@
         <v>1236</v>
       </c>
       <c r="G298">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="H298" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I298" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
@@ -13117,13 +13117,13 @@
         <v>1240</v>
       </c>
       <c r="G299">
-        <v>142</v>
+        <v>318</v>
       </c>
       <c r="H299" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I299" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
@@ -13146,13 +13146,13 @@
         <v>1244</v>
       </c>
       <c r="G300">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="H300" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I300" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
@@ -13175,13 +13175,13 @@
         <v>1248</v>
       </c>
       <c r="G301">
-        <v>185</v>
+        <v>132</v>
       </c>
       <c r="H301" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I301" t="s">
-        <v>931</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/selenium_testing/test_reports/travix_300_selenium_report.xlsx
+++ b/selenium_testing/test_reports/travix_300_selenium_report.xlsx
@@ -20,7 +20,7 @@
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>8/18/2026, 5:55:28 AM</t>
+    <t>8/18/2026, 6:20:30 AM</t>
   </si>
   <si>
     <t>Target Browser:</t>
@@ -155,7 +155,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-18T05:55:28.282Z</t>
+    <t>2026-08-18T06:20:30.623Z</t>
   </si>
   <si>
     <t>TC-SEL-UI-002</t>
@@ -170,9 +170,6 @@
     <t>Brand Shield Logo Animation rendered cleanly with correct padding, font scaling, and visual contrast</t>
   </si>
   <si>
-    <t>2026-08-18T05:55:28.283Z</t>
-  </si>
-  <si>
     <t>TC-SEL-UI-003</t>
   </si>
   <si>
@@ -1974,6 +1971,9 @@
   </si>
   <si>
     <t>Functional web scenario Verifying CORS header configuration completed successfully with zero state discrepancies</t>
+  </si>
+  <si>
+    <t>2026-08-18T06:20:30.624Z</t>
   </si>
   <si>
     <t>TC-SEL-FUNC-093</t>
@@ -4504,7 +4504,7 @@
         <v>45</v>
       </c>
       <c r="G2">
-        <v>166</v>
+        <v>334</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>46</v>
@@ -4533,18 +4533,18 @@
         <v>51</v>
       </c>
       <c r="G3">
-        <v>371</v>
+        <v>423</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -4553,27 +4553,27 @@
         <v>42</v>
       </c>
       <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" t="s">
         <v>54</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>55</v>
       </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
       <c r="G4">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -4582,27 +4582,27 @@
         <v>42</v>
       </c>
       <c r="D5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" t="s">
         <v>58</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>59</v>
       </c>
-      <c r="F5" t="s">
-        <v>60</v>
-      </c>
       <c r="G5">
-        <v>231</v>
+        <v>283</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -4611,27 +4611,27 @@
         <v>42</v>
       </c>
       <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
         <v>62</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>63</v>
       </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
       <c r="G6">
-        <v>189</v>
+        <v>484</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
@@ -4640,27 +4640,27 @@
         <v>42</v>
       </c>
       <c r="D7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" t="s">
         <v>66</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>67</v>
       </c>
-      <c r="F7" t="s">
-        <v>68</v>
-      </c>
       <c r="G7">
-        <v>406</v>
+        <v>541</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I7" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -4669,27 +4669,27 @@
         <v>42</v>
       </c>
       <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" t="s">
         <v>70</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>71</v>
       </c>
-      <c r="F8" t="s">
-        <v>72</v>
-      </c>
       <c r="G8">
-        <v>529</v>
+        <v>171</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
@@ -4698,27 +4698,27 @@
         <v>42</v>
       </c>
       <c r="D9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" t="s">
         <v>74</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>75</v>
       </c>
-      <c r="F9" t="s">
-        <v>76</v>
-      </c>
       <c r="G9">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
@@ -4727,27 +4727,27 @@
         <v>42</v>
       </c>
       <c r="D10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" t="s">
         <v>78</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>79</v>
       </c>
-      <c r="F10" t="s">
-        <v>80</v>
-      </c>
       <c r="G10">
-        <v>407</v>
+        <v>446</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I10" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
         <v>23</v>
@@ -4756,27 +4756,27 @@
         <v>42</v>
       </c>
       <c r="D11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" t="s">
         <v>82</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>83</v>
       </c>
-      <c r="F11" t="s">
-        <v>84</v>
-      </c>
       <c r="G11">
-        <v>233</v>
+        <v>507</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
@@ -4785,27 +4785,27 @@
         <v>42</v>
       </c>
       <c r="D12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" t="s">
         <v>86</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>87</v>
       </c>
-      <c r="F12" t="s">
-        <v>88</v>
-      </c>
       <c r="G12">
-        <v>480</v>
+        <v>224</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I12" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
@@ -4814,27 +4814,27 @@
         <v>42</v>
       </c>
       <c r="D13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" t="s">
         <v>90</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>91</v>
       </c>
-      <c r="F13" t="s">
-        <v>92</v>
-      </c>
       <c r="G13">
-        <v>181</v>
+        <v>408</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I13" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
@@ -4843,27 +4843,27 @@
         <v>42</v>
       </c>
       <c r="D14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" t="s">
         <v>94</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>95</v>
       </c>
-      <c r="F14" t="s">
-        <v>96</v>
-      </c>
       <c r="G14">
-        <v>543</v>
+        <v>276</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I14" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
@@ -4872,27 +4872,27 @@
         <v>42</v>
       </c>
       <c r="D15" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" t="s">
         <v>98</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>99</v>
       </c>
-      <c r="F15" t="s">
-        <v>100</v>
-      </c>
       <c r="G15">
-        <v>374</v>
+        <v>313</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I15" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
@@ -4901,27 +4901,27 @@
         <v>42</v>
       </c>
       <c r="D16" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" t="s">
         <v>102</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>103</v>
       </c>
-      <c r="F16" t="s">
-        <v>104</v>
-      </c>
       <c r="G16">
-        <v>303</v>
+        <v>191</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I16" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
@@ -4930,27 +4930,27 @@
         <v>42</v>
       </c>
       <c r="D17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" t="s">
         <v>106</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>107</v>
       </c>
-      <c r="F17" t="s">
-        <v>108</v>
-      </c>
       <c r="G17">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I17" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
@@ -4959,27 +4959,27 @@
         <v>42</v>
       </c>
       <c r="D18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" t="s">
         <v>110</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>111</v>
       </c>
-      <c r="F18" t="s">
-        <v>112</v>
-      </c>
       <c r="G18">
-        <v>411</v>
+        <v>456</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I18" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
@@ -4988,27 +4988,27 @@
         <v>42</v>
       </c>
       <c r="D19" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" t="s">
         <v>114</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>115</v>
       </c>
-      <c r="F19" t="s">
-        <v>116</v>
-      </c>
       <c r="G19">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I19" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -5017,27 +5017,27 @@
         <v>42</v>
       </c>
       <c r="D20" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" t="s">
         <v>118</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>119</v>
       </c>
-      <c r="F20" t="s">
-        <v>120</v>
-      </c>
       <c r="G20">
-        <v>383</v>
+        <v>222</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I20" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
@@ -5046,27 +5046,27 @@
         <v>42</v>
       </c>
       <c r="D21" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" t="s">
         <v>122</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>123</v>
       </c>
-      <c r="F21" t="s">
-        <v>124</v>
-      </c>
       <c r="G21">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I21" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
@@ -5075,27 +5075,27 @@
         <v>42</v>
       </c>
       <c r="D22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" t="s">
         <v>126</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>127</v>
       </c>
-      <c r="F22" t="s">
-        <v>128</v>
-      </c>
       <c r="G22">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="H22" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I22" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
@@ -5104,27 +5104,27 @@
         <v>42</v>
       </c>
       <c r="D23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" t="s">
         <v>130</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>131</v>
       </c>
-      <c r="F23" t="s">
-        <v>132</v>
-      </c>
       <c r="G23">
-        <v>257</v>
+        <v>487</v>
       </c>
       <c r="H23" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -5133,27 +5133,27 @@
         <v>42</v>
       </c>
       <c r="D24" t="s">
+        <v>133</v>
+      </c>
+      <c r="E24" t="s">
         <v>134</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>135</v>
       </c>
-      <c r="F24" t="s">
-        <v>136</v>
-      </c>
       <c r="G24">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="H24" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I24" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B25" t="s">
         <v>23</v>
@@ -5162,27 +5162,27 @@
         <v>42</v>
       </c>
       <c r="D25" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" t="s">
         <v>138</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>139</v>
       </c>
-      <c r="F25" t="s">
-        <v>140</v>
-      </c>
       <c r="G25">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="H25" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I25" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
@@ -5191,27 +5191,27 @@
         <v>42</v>
       </c>
       <c r="D26" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" t="s">
         <v>142</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>143</v>
       </c>
-      <c r="F26" t="s">
-        <v>144</v>
-      </c>
       <c r="G26">
-        <v>203</v>
+        <v>279</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I26" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B27" t="s">
         <v>23</v>
@@ -5220,27 +5220,27 @@
         <v>42</v>
       </c>
       <c r="D27" t="s">
+        <v>145</v>
+      </c>
+      <c r="E27" t="s">
         <v>146</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>147</v>
       </c>
-      <c r="F27" t="s">
-        <v>148</v>
-      </c>
       <c r="G27">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I27" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B28" t="s">
         <v>23</v>
@@ -5249,27 +5249,27 @@
         <v>42</v>
       </c>
       <c r="D28" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28" t="s">
         <v>150</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>151</v>
       </c>
-      <c r="F28" t="s">
-        <v>152</v>
-      </c>
       <c r="G28">
-        <v>495</v>
+        <v>375</v>
       </c>
       <c r="H28" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I28" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B29" t="s">
         <v>23</v>
@@ -5278,27 +5278,27 @@
         <v>42</v>
       </c>
       <c r="D29" t="s">
+        <v>153</v>
+      </c>
+      <c r="E29" t="s">
         <v>154</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>155</v>
       </c>
-      <c r="F29" t="s">
-        <v>156</v>
-      </c>
       <c r="G29">
-        <v>274</v>
+        <v>515</v>
       </c>
       <c r="H29" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I29" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B30" t="s">
         <v>23</v>
@@ -5307,27 +5307,27 @@
         <v>42</v>
       </c>
       <c r="D30" t="s">
+        <v>157</v>
+      </c>
+      <c r="E30" t="s">
         <v>158</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>159</v>
       </c>
-      <c r="F30" t="s">
-        <v>160</v>
-      </c>
       <c r="G30">
-        <v>259</v>
+        <v>316</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I30" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B31" t="s">
         <v>23</v>
@@ -5336,27 +5336,27 @@
         <v>42</v>
       </c>
       <c r="D31" t="s">
+        <v>161</v>
+      </c>
+      <c r="E31" t="s">
         <v>162</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>163</v>
       </c>
-      <c r="F31" t="s">
-        <v>164</v>
-      </c>
       <c r="G31">
-        <v>347</v>
+        <v>316</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I31" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B32" t="s">
         <v>23</v>
@@ -5365,27 +5365,27 @@
         <v>42</v>
       </c>
       <c r="D32" t="s">
+        <v>165</v>
+      </c>
+      <c r="E32" t="s">
         <v>166</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>167</v>
       </c>
-      <c r="F32" t="s">
-        <v>168</v>
-      </c>
       <c r="G32">
-        <v>516</v>
+        <v>379</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I32" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B33" t="s">
         <v>23</v>
@@ -5394,27 +5394,27 @@
         <v>42</v>
       </c>
       <c r="D33" t="s">
+        <v>169</v>
+      </c>
+      <c r="E33" t="s">
         <v>170</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>171</v>
       </c>
-      <c r="F33" t="s">
-        <v>172</v>
-      </c>
       <c r="G33">
-        <v>528</v>
+        <v>210</v>
       </c>
       <c r="H33" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I33" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B34" t="s">
         <v>23</v>
@@ -5423,27 +5423,27 @@
         <v>42</v>
       </c>
       <c r="D34" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" t="s">
         <v>174</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>175</v>
       </c>
-      <c r="F34" t="s">
-        <v>176</v>
-      </c>
       <c r="G34">
-        <v>251</v>
+        <v>428</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I34" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s">
         <v>23</v>
@@ -5452,27 +5452,27 @@
         <v>42</v>
       </c>
       <c r="D35" t="s">
+        <v>177</v>
+      </c>
+      <c r="E35" t="s">
         <v>178</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>179</v>
       </c>
-      <c r="F35" t="s">
-        <v>180</v>
-      </c>
       <c r="G35">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="H35" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I35" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B36" t="s">
         <v>23</v>
@@ -5481,27 +5481,27 @@
         <v>42</v>
       </c>
       <c r="D36" t="s">
+        <v>181</v>
+      </c>
+      <c r="E36" t="s">
         <v>182</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>183</v>
       </c>
-      <c r="F36" t="s">
-        <v>184</v>
-      </c>
       <c r="G36">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="H36" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I36" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B37" t="s">
         <v>23</v>
@@ -5510,27 +5510,27 @@
         <v>42</v>
       </c>
       <c r="D37" t="s">
+        <v>185</v>
+      </c>
+      <c r="E37" t="s">
         <v>186</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>187</v>
       </c>
-      <c r="F37" t="s">
-        <v>188</v>
-      </c>
       <c r="G37">
-        <v>364</v>
+        <v>408</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I37" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B38" t="s">
         <v>23</v>
@@ -5539,27 +5539,27 @@
         <v>42</v>
       </c>
       <c r="D38" t="s">
+        <v>189</v>
+      </c>
+      <c r="E38" t="s">
         <v>190</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>191</v>
       </c>
-      <c r="F38" t="s">
-        <v>192</v>
-      </c>
       <c r="G38">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I38" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B39" t="s">
         <v>23</v>
@@ -5568,27 +5568,27 @@
         <v>42</v>
       </c>
       <c r="D39" t="s">
+        <v>193</v>
+      </c>
+      <c r="E39" t="s">
         <v>194</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>195</v>
       </c>
-      <c r="F39" t="s">
-        <v>196</v>
-      </c>
       <c r="G39">
-        <v>246</v>
+        <v>432</v>
       </c>
       <c r="H39" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I39" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B40" t="s">
         <v>23</v>
@@ -5597,27 +5597,27 @@
         <v>42</v>
       </c>
       <c r="D40" t="s">
+        <v>197</v>
+      </c>
+      <c r="E40" t="s">
         <v>198</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>199</v>
       </c>
-      <c r="F40" t="s">
-        <v>200</v>
-      </c>
       <c r="G40">
-        <v>196</v>
+        <v>404</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I40" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B41" t="s">
         <v>23</v>
@@ -5626,27 +5626,27 @@
         <v>42</v>
       </c>
       <c r="D41" t="s">
+        <v>201</v>
+      </c>
+      <c r="E41" t="s">
         <v>202</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>203</v>
       </c>
-      <c r="F41" t="s">
-        <v>204</v>
-      </c>
       <c r="G41">
-        <v>506</v>
+        <v>165</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I41" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s">
         <v>23</v>
@@ -5655,27 +5655,27 @@
         <v>42</v>
       </c>
       <c r="D42" t="s">
+        <v>205</v>
+      </c>
+      <c r="E42" t="s">
         <v>206</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>207</v>
       </c>
-      <c r="F42" t="s">
-        <v>208</v>
-      </c>
       <c r="G42">
-        <v>464</v>
+        <v>388</v>
       </c>
       <c r="H42" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I42" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B43" t="s">
         <v>23</v>
@@ -5684,27 +5684,27 @@
         <v>42</v>
       </c>
       <c r="D43" t="s">
+        <v>209</v>
+      </c>
+      <c r="E43" t="s">
         <v>210</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>211</v>
       </c>
-      <c r="F43" t="s">
-        <v>212</v>
-      </c>
       <c r="G43">
-        <v>318</v>
+        <v>496</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I43" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B44" t="s">
         <v>23</v>
@@ -5713,27 +5713,27 @@
         <v>42</v>
       </c>
       <c r="D44" t="s">
+        <v>213</v>
+      </c>
+      <c r="E44" t="s">
         <v>214</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>215</v>
       </c>
-      <c r="F44" t="s">
-        <v>216</v>
-      </c>
       <c r="G44">
-        <v>302</v>
+        <v>410</v>
       </c>
       <c r="H44" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I44" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B45" t="s">
         <v>23</v>
@@ -5742,27 +5742,27 @@
         <v>42</v>
       </c>
       <c r="D45" t="s">
+        <v>217</v>
+      </c>
+      <c r="E45" t="s">
         <v>218</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>219</v>
       </c>
-      <c r="F45" t="s">
-        <v>220</v>
-      </c>
       <c r="G45">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="H45" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I45" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B46" t="s">
         <v>23</v>
@@ -5771,27 +5771,27 @@
         <v>42</v>
       </c>
       <c r="D46" t="s">
+        <v>221</v>
+      </c>
+      <c r="E46" t="s">
         <v>222</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>223</v>
       </c>
-      <c r="F46" t="s">
-        <v>224</v>
-      </c>
       <c r="G46">
-        <v>537</v>
+        <v>413</v>
       </c>
       <c r="H46" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I46" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B47" t="s">
         <v>23</v>
@@ -5800,27 +5800,27 @@
         <v>42</v>
       </c>
       <c r="D47" t="s">
+        <v>225</v>
+      </c>
+      <c r="E47" t="s">
         <v>226</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>227</v>
       </c>
-      <c r="F47" t="s">
-        <v>228</v>
-      </c>
       <c r="G47">
-        <v>318</v>
+        <v>535</v>
       </c>
       <c r="H47" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I47" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B48" t="s">
         <v>23</v>
@@ -5829,27 +5829,27 @@
         <v>42</v>
       </c>
       <c r="D48" t="s">
+        <v>229</v>
+      </c>
+      <c r="E48" t="s">
         <v>230</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>231</v>
       </c>
-      <c r="F48" t="s">
-        <v>232</v>
-      </c>
       <c r="G48">
-        <v>545</v>
+        <v>151</v>
       </c>
       <c r="H48" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I48" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B49" t="s">
         <v>23</v>
@@ -5858,27 +5858,27 @@
         <v>42</v>
       </c>
       <c r="D49" t="s">
+        <v>233</v>
+      </c>
+      <c r="E49" t="s">
         <v>234</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>235</v>
       </c>
-      <c r="F49" t="s">
-        <v>236</v>
-      </c>
       <c r="G49">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I49" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B50" t="s">
         <v>23</v>
@@ -5887,27 +5887,27 @@
         <v>42</v>
       </c>
       <c r="D50" t="s">
+        <v>237</v>
+      </c>
+      <c r="E50" t="s">
         <v>238</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>239</v>
       </c>
-      <c r="F50" t="s">
-        <v>240</v>
-      </c>
       <c r="G50">
-        <v>267</v>
+        <v>169</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I50" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B51" t="s">
         <v>23</v>
@@ -5916,27 +5916,27 @@
         <v>42</v>
       </c>
       <c r="D51" t="s">
+        <v>241</v>
+      </c>
+      <c r="E51" t="s">
         <v>242</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>243</v>
       </c>
-      <c r="F51" t="s">
-        <v>244</v>
-      </c>
       <c r="G51">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="H51" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I51" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B52" t="s">
         <v>23</v>
@@ -5945,27 +5945,27 @@
         <v>42</v>
       </c>
       <c r="D52" t="s">
+        <v>245</v>
+      </c>
+      <c r="E52" t="s">
         <v>246</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>247</v>
       </c>
-      <c r="F52" t="s">
-        <v>248</v>
-      </c>
       <c r="G52">
-        <v>167</v>
+        <v>468</v>
       </c>
       <c r="H52" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I52" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B53" t="s">
         <v>23</v>
@@ -5974,27 +5974,27 @@
         <v>42</v>
       </c>
       <c r="D53" t="s">
+        <v>249</v>
+      </c>
+      <c r="E53" t="s">
         <v>250</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>251</v>
       </c>
-      <c r="F53" t="s">
-        <v>252</v>
-      </c>
       <c r="G53">
-        <v>342</v>
+        <v>218</v>
       </c>
       <c r="H53" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I53" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B54" t="s">
         <v>23</v>
@@ -6003,27 +6003,27 @@
         <v>42</v>
       </c>
       <c r="D54" t="s">
+        <v>253</v>
+      </c>
+      <c r="E54" t="s">
         <v>254</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>255</v>
       </c>
-      <c r="F54" t="s">
-        <v>256</v>
-      </c>
       <c r="G54">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="H54" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I54" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B55" t="s">
         <v>23</v>
@@ -6032,27 +6032,27 @@
         <v>42</v>
       </c>
       <c r="D55" t="s">
+        <v>257</v>
+      </c>
+      <c r="E55" t="s">
         <v>258</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>259</v>
       </c>
-      <c r="F55" t="s">
-        <v>260</v>
-      </c>
       <c r="G55">
-        <v>182</v>
+        <v>471</v>
       </c>
       <c r="H55" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I55" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B56" t="s">
         <v>23</v>
@@ -6061,27 +6061,27 @@
         <v>42</v>
       </c>
       <c r="D56" t="s">
+        <v>261</v>
+      </c>
+      <c r="E56" t="s">
         <v>262</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>263</v>
       </c>
-      <c r="F56" t="s">
-        <v>264</v>
-      </c>
       <c r="G56">
-        <v>526</v>
+        <v>452</v>
       </c>
       <c r="H56" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I56" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B57" t="s">
         <v>23</v>
@@ -6090,27 +6090,27 @@
         <v>42</v>
       </c>
       <c r="D57" t="s">
+        <v>265</v>
+      </c>
+      <c r="E57" t="s">
         <v>266</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>267</v>
       </c>
-      <c r="F57" t="s">
-        <v>268</v>
-      </c>
       <c r="G57">
-        <v>268</v>
+        <v>221</v>
       </c>
       <c r="H57" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I57" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B58" t="s">
         <v>23</v>
@@ -6119,27 +6119,27 @@
         <v>42</v>
       </c>
       <c r="D58" t="s">
+        <v>269</v>
+      </c>
+      <c r="E58" t="s">
         <v>270</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>271</v>
       </c>
-      <c r="F58" t="s">
-        <v>272</v>
-      </c>
       <c r="G58">
-        <v>531</v>
+        <v>439</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I58" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B59" t="s">
         <v>23</v>
@@ -6148,27 +6148,27 @@
         <v>42</v>
       </c>
       <c r="D59" t="s">
+        <v>273</v>
+      </c>
+      <c r="E59" t="s">
         <v>274</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>275</v>
       </c>
-      <c r="F59" t="s">
-        <v>276</v>
-      </c>
       <c r="G59">
-        <v>543</v>
+        <v>266</v>
       </c>
       <c r="H59" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I59" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B60" t="s">
         <v>23</v>
@@ -6177,27 +6177,27 @@
         <v>42</v>
       </c>
       <c r="D60" t="s">
+        <v>277</v>
+      </c>
+      <c r="E60" t="s">
         <v>278</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>279</v>
       </c>
-      <c r="F60" t="s">
-        <v>280</v>
-      </c>
       <c r="G60">
-        <v>491</v>
+        <v>232</v>
       </c>
       <c r="H60" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I60" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B61" t="s">
         <v>23</v>
@@ -6206,2690 +6206,2690 @@
         <v>42</v>
       </c>
       <c r="D61" t="s">
+        <v>281</v>
+      </c>
+      <c r="E61" t="s">
         <v>282</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>283</v>
       </c>
-      <c r="F61" t="s">
-        <v>284</v>
-      </c>
       <c r="G61">
-        <v>457</v>
+        <v>420</v>
       </c>
       <c r="H61" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I61" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B62" t="s">
         <v>25</v>
       </c>
       <c r="C62" t="s">
+        <v>285</v>
+      </c>
+      <c r="D62" t="s">
         <v>286</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>287</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>288</v>
       </c>
-      <c r="F62" t="s">
-        <v>289</v>
-      </c>
       <c r="G62">
-        <v>419</v>
+        <v>454</v>
       </c>
       <c r="H62" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I62" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B63" t="s">
         <v>25</v>
       </c>
       <c r="C63" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D63" t="s">
+        <v>290</v>
+      </c>
+      <c r="E63" t="s">
         <v>291</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>292</v>
       </c>
-      <c r="F63" t="s">
-        <v>293</v>
-      </c>
       <c r="G63">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="H63" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I63" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B64" t="s">
         <v>25</v>
       </c>
       <c r="C64" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D64" t="s">
+        <v>294</v>
+      </c>
+      <c r="E64" t="s">
         <v>295</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>296</v>
       </c>
-      <c r="F64" t="s">
-        <v>297</v>
-      </c>
       <c r="G64">
-        <v>787</v>
+        <v>715</v>
       </c>
       <c r="H64" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I64" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B65" t="s">
         <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D65" t="s">
+        <v>298</v>
+      </c>
+      <c r="E65" t="s">
         <v>299</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>300</v>
       </c>
-      <c r="F65" t="s">
-        <v>301</v>
-      </c>
       <c r="G65">
-        <v>634</v>
+        <v>607</v>
       </c>
       <c r="H65" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I65" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B66" t="s">
         <v>25</v>
       </c>
       <c r="C66" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D66" t="s">
+        <v>302</v>
+      </c>
+      <c r="E66" t="s">
         <v>303</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>304</v>
       </c>
-      <c r="F66" t="s">
-        <v>305</v>
-      </c>
       <c r="G66">
-        <v>343</v>
+        <v>387</v>
       </c>
       <c r="H66" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I66" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B67" t="s">
         <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D67" t="s">
+        <v>306</v>
+      </c>
+      <c r="E67" t="s">
         <v>307</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>308</v>
       </c>
-      <c r="F67" t="s">
-        <v>309</v>
-      </c>
       <c r="G67">
-        <v>665</v>
+        <v>387</v>
       </c>
       <c r="H67" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I67" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B68" t="s">
         <v>25</v>
       </c>
       <c r="C68" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D68" t="s">
+        <v>310</v>
+      </c>
+      <c r="E68" t="s">
         <v>311</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>312</v>
       </c>
-      <c r="F68" t="s">
-        <v>313</v>
-      </c>
       <c r="G68">
-        <v>534</v>
+        <v>291</v>
       </c>
       <c r="H68" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I68" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B69" t="s">
         <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D69" t="s">
+        <v>314</v>
+      </c>
+      <c r="E69" t="s">
         <v>315</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>316</v>
       </c>
-      <c r="F69" t="s">
-        <v>317</v>
-      </c>
       <c r="G69">
-        <v>496</v>
+        <v>424</v>
       </c>
       <c r="H69" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I69" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B70" t="s">
         <v>25</v>
       </c>
       <c r="C70" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D70" t="s">
+        <v>318</v>
+      </c>
+      <c r="E70" t="s">
         <v>319</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>320</v>
       </c>
-      <c r="F70" t="s">
-        <v>321</v>
-      </c>
       <c r="G70">
-        <v>346</v>
+        <v>621</v>
       </c>
       <c r="H70" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I70" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B71" t="s">
         <v>25</v>
       </c>
       <c r="C71" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D71" t="s">
+        <v>322</v>
+      </c>
+      <c r="E71" t="s">
         <v>323</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>324</v>
       </c>
-      <c r="F71" t="s">
-        <v>325</v>
-      </c>
       <c r="G71">
-        <v>776</v>
+        <v>398</v>
       </c>
       <c r="H71" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I71" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B72" t="s">
         <v>25</v>
       </c>
       <c r="C72" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D72" t="s">
+        <v>326</v>
+      </c>
+      <c r="E72" t="s">
         <v>327</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>328</v>
       </c>
-      <c r="F72" t="s">
-        <v>329</v>
-      </c>
       <c r="G72">
-        <v>432</v>
+        <v>338</v>
       </c>
       <c r="H72" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I72" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B73" t="s">
         <v>25</v>
       </c>
       <c r="C73" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D73" t="s">
+        <v>330</v>
+      </c>
+      <c r="E73" t="s">
         <v>331</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>332</v>
       </c>
-      <c r="F73" t="s">
-        <v>333</v>
-      </c>
       <c r="G73">
-        <v>264</v>
+        <v>577</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I73" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B74" t="s">
         <v>25</v>
       </c>
       <c r="C74" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D74" t="s">
+        <v>334</v>
+      </c>
+      <c r="E74" t="s">
         <v>335</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>336</v>
       </c>
-      <c r="F74" t="s">
-        <v>337</v>
-      </c>
       <c r="G74">
-        <v>370</v>
+        <v>753</v>
       </c>
       <c r="H74" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I74" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B75" t="s">
         <v>25</v>
       </c>
       <c r="C75" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D75" t="s">
+        <v>338</v>
+      </c>
+      <c r="E75" t="s">
         <v>339</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>340</v>
       </c>
-      <c r="F75" t="s">
-        <v>341</v>
-      </c>
       <c r="G75">
-        <v>502</v>
+        <v>711</v>
       </c>
       <c r="H75" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I75" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B76" t="s">
         <v>25</v>
       </c>
       <c r="C76" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D76" t="s">
+        <v>342</v>
+      </c>
+      <c r="E76" t="s">
         <v>343</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>344</v>
       </c>
-      <c r="F76" t="s">
-        <v>345</v>
-      </c>
       <c r="G76">
-        <v>606</v>
+        <v>264</v>
       </c>
       <c r="H76" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I76" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B77" t="s">
         <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D77" t="s">
+        <v>346</v>
+      </c>
+      <c r="E77" t="s">
         <v>347</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>348</v>
       </c>
-      <c r="F77" t="s">
-        <v>349</v>
-      </c>
       <c r="G77">
-        <v>653</v>
+        <v>722</v>
       </c>
       <c r="H77" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I77" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B78" t="s">
         <v>25</v>
       </c>
       <c r="C78" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D78" t="s">
+        <v>350</v>
+      </c>
+      <c r="E78" t="s">
         <v>351</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>352</v>
       </c>
-      <c r="F78" t="s">
-        <v>353</v>
-      </c>
       <c r="G78">
-        <v>300</v>
+        <v>768</v>
       </c>
       <c r="H78" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I78" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B79" t="s">
         <v>25</v>
       </c>
       <c r="C79" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D79" t="s">
+        <v>354</v>
+      </c>
+      <c r="E79" t="s">
         <v>355</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>356</v>
       </c>
-      <c r="F79" t="s">
-        <v>357</v>
-      </c>
       <c r="G79">
-        <v>595</v>
+        <v>469</v>
       </c>
       <c r="H79" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I79" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B80" t="s">
         <v>25</v>
       </c>
       <c r="C80" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D80" t="s">
+        <v>358</v>
+      </c>
+      <c r="E80" t="s">
         <v>359</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>360</v>
       </c>
-      <c r="F80" t="s">
-        <v>361</v>
-      </c>
       <c r="G80">
-        <v>632</v>
+        <v>406</v>
       </c>
       <c r="H80" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I80" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B81" t="s">
         <v>25</v>
       </c>
       <c r="C81" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D81" t="s">
+        <v>362</v>
+      </c>
+      <c r="E81" t="s">
         <v>363</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>364</v>
       </c>
-      <c r="F81" t="s">
-        <v>365</v>
-      </c>
       <c r="G81">
-        <v>614</v>
+        <v>373</v>
       </c>
       <c r="H81" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I81" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B82" t="s">
         <v>25</v>
       </c>
       <c r="C82" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D82" t="s">
+        <v>366</v>
+      </c>
+      <c r="E82" t="s">
         <v>367</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>368</v>
       </c>
-      <c r="F82" t="s">
-        <v>369</v>
-      </c>
       <c r="G82">
-        <v>678</v>
+        <v>758</v>
       </c>
       <c r="H82" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I82" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B83" t="s">
         <v>25</v>
       </c>
       <c r="C83" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D83" t="s">
+        <v>370</v>
+      </c>
+      <c r="E83" t="s">
         <v>371</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>372</v>
       </c>
-      <c r="F83" t="s">
-        <v>373</v>
-      </c>
       <c r="G83">
-        <v>482</v>
+        <v>647</v>
       </c>
       <c r="H83" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I83" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B84" t="s">
         <v>25</v>
       </c>
       <c r="C84" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D84" t="s">
+        <v>374</v>
+      </c>
+      <c r="E84" t="s">
         <v>375</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>376</v>
       </c>
-      <c r="F84" t="s">
-        <v>377</v>
-      </c>
       <c r="G84">
-        <v>540</v>
+        <v>768</v>
       </c>
       <c r="H84" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I84" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B85" t="s">
         <v>25</v>
       </c>
       <c r="C85" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D85" t="s">
+        <v>378</v>
+      </c>
+      <c r="E85" t="s">
         <v>379</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>380</v>
       </c>
-      <c r="F85" t="s">
-        <v>381</v>
-      </c>
       <c r="G85">
-        <v>552</v>
+        <v>687</v>
       </c>
       <c r="H85" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I85" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B86" t="s">
         <v>25</v>
       </c>
       <c r="C86" t="s">
+        <v>285</v>
+      </c>
+      <c r="D86" t="s">
+        <v>382</v>
+      </c>
+      <c r="E86" t="s">
+        <v>383</v>
+      </c>
+      <c r="F86" t="s">
+        <v>384</v>
+      </c>
+      <c r="G86">
         <v>286</v>
       </c>
-      <c r="D86" t="s">
-        <v>383</v>
-      </c>
-      <c r="E86" t="s">
-        <v>384</v>
-      </c>
-      <c r="F86" t="s">
-        <v>385</v>
-      </c>
-      <c r="G86">
-        <v>398</v>
-      </c>
       <c r="H86" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I86" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B87" t="s">
         <v>25</v>
       </c>
       <c r="C87" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D87" t="s">
+        <v>386</v>
+      </c>
+      <c r="E87" t="s">
         <v>387</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>388</v>
       </c>
-      <c r="F87" t="s">
-        <v>389</v>
-      </c>
       <c r="G87">
-        <v>633</v>
+        <v>603</v>
       </c>
       <c r="H87" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I87" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B88" t="s">
         <v>25</v>
       </c>
       <c r="C88" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D88" t="s">
+        <v>390</v>
+      </c>
+      <c r="E88" t="s">
         <v>391</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>392</v>
       </c>
-      <c r="F88" t="s">
-        <v>393</v>
-      </c>
       <c r="G88">
-        <v>645</v>
+        <v>352</v>
       </c>
       <c r="H88" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I88" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B89" t="s">
         <v>25</v>
       </c>
       <c r="C89" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D89" t="s">
+        <v>394</v>
+      </c>
+      <c r="E89" t="s">
         <v>395</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>396</v>
       </c>
-      <c r="F89" t="s">
-        <v>397</v>
-      </c>
       <c r="G89">
-        <v>712</v>
+        <v>503</v>
       </c>
       <c r="H89" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I89" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B90" t="s">
         <v>25</v>
       </c>
       <c r="C90" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D90" t="s">
+        <v>398</v>
+      </c>
+      <c r="E90" t="s">
         <v>399</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>400</v>
       </c>
-      <c r="F90" t="s">
-        <v>401</v>
-      </c>
       <c r="G90">
-        <v>458</v>
+        <v>296</v>
       </c>
       <c r="H90" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I90" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B91" t="s">
         <v>25</v>
       </c>
       <c r="C91" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D91" t="s">
+        <v>402</v>
+      </c>
+      <c r="E91" t="s">
         <v>403</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>404</v>
       </c>
-      <c r="F91" t="s">
-        <v>405</v>
-      </c>
       <c r="G91">
-        <v>398</v>
+        <v>307</v>
       </c>
       <c r="H91" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I91" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B92" t="s">
         <v>25</v>
       </c>
       <c r="C92" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D92" t="s">
+        <v>406</v>
+      </c>
+      <c r="E92" t="s">
         <v>407</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>408</v>
       </c>
-      <c r="F92" t="s">
-        <v>409</v>
-      </c>
       <c r="G92">
-        <v>633</v>
+        <v>594</v>
       </c>
       <c r="H92" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I92" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B93" t="s">
         <v>25</v>
       </c>
       <c r="C93" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D93" t="s">
+        <v>410</v>
+      </c>
+      <c r="E93" t="s">
         <v>411</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>412</v>
       </c>
-      <c r="F93" t="s">
-        <v>413</v>
-      </c>
       <c r="G93">
-        <v>768</v>
+        <v>750</v>
       </c>
       <c r="H93" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I93" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B94" t="s">
         <v>25</v>
       </c>
       <c r="C94" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D94" t="s">
+        <v>414</v>
+      </c>
+      <c r="E94" t="s">
         <v>415</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>416</v>
       </c>
-      <c r="F94" t="s">
-        <v>417</v>
-      </c>
       <c r="G94">
-        <v>420</v>
+        <v>319</v>
       </c>
       <c r="H94" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I94" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B95" t="s">
         <v>25</v>
       </c>
       <c r="C95" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D95" t="s">
+        <v>418</v>
+      </c>
+      <c r="E95" t="s">
         <v>419</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
         <v>420</v>
       </c>
-      <c r="F95" t="s">
-        <v>421</v>
-      </c>
       <c r="G95">
-        <v>772</v>
+        <v>612</v>
       </c>
       <c r="H95" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I95" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B96" t="s">
         <v>25</v>
       </c>
       <c r="C96" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D96" t="s">
+        <v>422</v>
+      </c>
+      <c r="E96" t="s">
         <v>423</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>424</v>
       </c>
-      <c r="F96" t="s">
-        <v>425</v>
-      </c>
       <c r="G96">
-        <v>283</v>
+        <v>773</v>
       </c>
       <c r="H96" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I96" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B97" t="s">
         <v>25</v>
       </c>
       <c r="C97" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D97" t="s">
+        <v>426</v>
+      </c>
+      <c r="E97" t="s">
         <v>427</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>428</v>
       </c>
-      <c r="F97" t="s">
-        <v>429</v>
-      </c>
       <c r="G97">
-        <v>555</v>
+        <v>636</v>
       </c>
       <c r="H97" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I97" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B98" t="s">
         <v>25</v>
       </c>
       <c r="C98" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D98" t="s">
+        <v>430</v>
+      </c>
+      <c r="E98" t="s">
         <v>431</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>432</v>
       </c>
-      <c r="F98" t="s">
-        <v>433</v>
-      </c>
       <c r="G98">
-        <v>545</v>
+        <v>347</v>
       </c>
       <c r="H98" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I98" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B99" t="s">
         <v>25</v>
       </c>
       <c r="C99" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D99" t="s">
+        <v>434</v>
+      </c>
+      <c r="E99" t="s">
         <v>435</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>436</v>
       </c>
-      <c r="F99" t="s">
-        <v>437</v>
-      </c>
       <c r="G99">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="H99" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I99" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B100" t="s">
         <v>25</v>
       </c>
       <c r="C100" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D100" t="s">
+        <v>438</v>
+      </c>
+      <c r="E100" t="s">
         <v>439</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>440</v>
       </c>
-      <c r="F100" t="s">
-        <v>441</v>
-      </c>
       <c r="G100">
-        <v>468</v>
+        <v>748</v>
       </c>
       <c r="H100" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I100" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B101" t="s">
         <v>25</v>
       </c>
       <c r="C101" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D101" t="s">
+        <v>442</v>
+      </c>
+      <c r="E101" t="s">
         <v>443</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>444</v>
       </c>
-      <c r="F101" t="s">
-        <v>445</v>
-      </c>
       <c r="G101">
-        <v>583</v>
+        <v>257</v>
       </c>
       <c r="H101" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I101" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B102" t="s">
         <v>25</v>
       </c>
       <c r="C102" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D102" t="s">
+        <v>446</v>
+      </c>
+      <c r="E102" t="s">
         <v>447</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>448</v>
       </c>
-      <c r="F102" t="s">
-        <v>449</v>
-      </c>
       <c r="G102">
-        <v>278</v>
+        <v>439</v>
       </c>
       <c r="H102" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I102" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B103" t="s">
         <v>25</v>
       </c>
       <c r="C103" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D103" t="s">
+        <v>450</v>
+      </c>
+      <c r="E103" t="s">
         <v>451</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>452</v>
       </c>
-      <c r="F103" t="s">
-        <v>453</v>
-      </c>
       <c r="G103">
-        <v>785</v>
+        <v>474</v>
       </c>
       <c r="H103" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I103" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B104" t="s">
         <v>25</v>
       </c>
       <c r="C104" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D104" t="s">
+        <v>454</v>
+      </c>
+      <c r="E104" t="s">
         <v>455</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>456</v>
       </c>
-      <c r="F104" t="s">
-        <v>457</v>
-      </c>
       <c r="G104">
-        <v>503</v>
+        <v>599</v>
       </c>
       <c r="H104" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I104" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B105" t="s">
         <v>25</v>
       </c>
       <c r="C105" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D105" t="s">
+        <v>458</v>
+      </c>
+      <c r="E105" t="s">
         <v>459</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>460</v>
       </c>
-      <c r="F105" t="s">
-        <v>461</v>
-      </c>
       <c r="G105">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="H105" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I105" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B106" t="s">
         <v>25</v>
       </c>
       <c r="C106" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D106" t="s">
+        <v>462</v>
+      </c>
+      <c r="E106" t="s">
         <v>463</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>464</v>
       </c>
-      <c r="F106" t="s">
-        <v>465</v>
-      </c>
       <c r="G106">
-        <v>493</v>
+        <v>779</v>
       </c>
       <c r="H106" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I106" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B107" t="s">
         <v>25</v>
       </c>
       <c r="C107" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D107" t="s">
+        <v>466</v>
+      </c>
+      <c r="E107" t="s">
         <v>467</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>468</v>
       </c>
-      <c r="F107" t="s">
-        <v>469</v>
-      </c>
       <c r="G107">
-        <v>448</v>
+        <v>257</v>
       </c>
       <c r="H107" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I107" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B108" t="s">
         <v>25</v>
       </c>
       <c r="C108" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D108" t="s">
+        <v>470</v>
+      </c>
+      <c r="E108" t="s">
         <v>471</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>472</v>
       </c>
-      <c r="F108" t="s">
-        <v>473</v>
-      </c>
       <c r="G108">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="H108" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I108" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B109" t="s">
         <v>25</v>
       </c>
       <c r="C109" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D109" t="s">
+        <v>474</v>
+      </c>
+      <c r="E109" t="s">
         <v>475</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>476</v>
       </c>
-      <c r="F109" t="s">
-        <v>477</v>
-      </c>
       <c r="G109">
-        <v>510</v>
+        <v>345</v>
       </c>
       <c r="H109" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I109" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B110" t="s">
         <v>25</v>
       </c>
       <c r="C110" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D110" t="s">
+        <v>478</v>
+      </c>
+      <c r="E110" t="s">
         <v>479</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>480</v>
       </c>
-      <c r="F110" t="s">
-        <v>481</v>
-      </c>
       <c r="G110">
-        <v>726</v>
+        <v>532</v>
       </c>
       <c r="H110" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I110" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B111" t="s">
         <v>25</v>
       </c>
       <c r="C111" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D111" t="s">
+        <v>482</v>
+      </c>
+      <c r="E111" t="s">
         <v>483</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
         <v>484</v>
       </c>
-      <c r="F111" t="s">
-        <v>485</v>
-      </c>
       <c r="G111">
-        <v>664</v>
+        <v>650</v>
       </c>
       <c r="H111" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I111" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B112" t="s">
         <v>25</v>
       </c>
       <c r="C112" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D112" t="s">
+        <v>486</v>
+      </c>
+      <c r="E112" t="s">
         <v>487</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>488</v>
       </c>
-      <c r="F112" t="s">
-        <v>489</v>
-      </c>
       <c r="G112">
-        <v>731</v>
+        <v>276</v>
       </c>
       <c r="H112" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I112" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B113" t="s">
         <v>25</v>
       </c>
       <c r="C113" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D113" t="s">
+        <v>490</v>
+      </c>
+      <c r="E113" t="s">
         <v>491</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
         <v>492</v>
       </c>
-      <c r="F113" t="s">
-        <v>493</v>
-      </c>
       <c r="G113">
-        <v>353</v>
+        <v>446</v>
       </c>
       <c r="H113" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I113" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B114" t="s">
         <v>25</v>
       </c>
       <c r="C114" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D114" t="s">
+        <v>494</v>
+      </c>
+      <c r="E114" t="s">
         <v>495</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>496</v>
       </c>
-      <c r="F114" t="s">
-        <v>497</v>
-      </c>
       <c r="G114">
-        <v>709</v>
+        <v>590</v>
       </c>
       <c r="H114" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I114" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B115" t="s">
         <v>25</v>
       </c>
       <c r="C115" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D115" t="s">
+        <v>498</v>
+      </c>
+      <c r="E115" t="s">
         <v>499</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>500</v>
       </c>
-      <c r="F115" t="s">
-        <v>501</v>
-      </c>
       <c r="G115">
-        <v>304</v>
+        <v>727</v>
       </c>
       <c r="H115" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I115" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B116" t="s">
         <v>25</v>
       </c>
       <c r="C116" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D116" t="s">
+        <v>502</v>
+      </c>
+      <c r="E116" t="s">
         <v>503</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>504</v>
       </c>
-      <c r="F116" t="s">
-        <v>505</v>
-      </c>
       <c r="G116">
-        <v>566</v>
+        <v>412</v>
       </c>
       <c r="H116" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I116" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B117" t="s">
         <v>25</v>
       </c>
       <c r="C117" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D117" t="s">
+        <v>506</v>
+      </c>
+      <c r="E117" t="s">
         <v>507</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>508</v>
       </c>
-      <c r="F117" t="s">
-        <v>509</v>
-      </c>
       <c r="G117">
-        <v>574</v>
+        <v>791</v>
       </c>
       <c r="H117" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I117" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B118" t="s">
         <v>25</v>
       </c>
       <c r="C118" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D118" t="s">
+        <v>510</v>
+      </c>
+      <c r="E118" t="s">
         <v>511</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
         <v>512</v>
       </c>
-      <c r="F118" t="s">
-        <v>513</v>
-      </c>
       <c r="G118">
-        <v>394</v>
+        <v>445</v>
       </c>
       <c r="H118" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I118" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B119" t="s">
         <v>25</v>
       </c>
       <c r="C119" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D119" t="s">
+        <v>514</v>
+      </c>
+      <c r="E119" t="s">
         <v>515</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>516</v>
       </c>
-      <c r="F119" t="s">
-        <v>517</v>
-      </c>
       <c r="G119">
-        <v>296</v>
+        <v>544</v>
       </c>
       <c r="H119" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I119" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B120" t="s">
         <v>25</v>
       </c>
       <c r="C120" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D120" t="s">
+        <v>518</v>
+      </c>
+      <c r="E120" t="s">
         <v>519</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
         <v>520</v>
       </c>
-      <c r="F120" t="s">
-        <v>521</v>
-      </c>
       <c r="G120">
-        <v>616</v>
+        <v>490</v>
       </c>
       <c r="H120" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I120" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B121" t="s">
         <v>25</v>
       </c>
       <c r="C121" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D121" t="s">
+        <v>522</v>
+      </c>
+      <c r="E121" t="s">
         <v>523</v>
       </c>
-      <c r="E121" t="s">
+      <c r="F121" t="s">
         <v>524</v>
       </c>
-      <c r="F121" t="s">
-        <v>525</v>
-      </c>
       <c r="G121">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="H121" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I121" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B122" t="s">
         <v>25</v>
       </c>
       <c r="C122" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D122" t="s">
+        <v>526</v>
+      </c>
+      <c r="E122" t="s">
         <v>527</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>528</v>
       </c>
-      <c r="F122" t="s">
-        <v>529</v>
-      </c>
       <c r="G122">
-        <v>575</v>
+        <v>306</v>
       </c>
       <c r="H122" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I122" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B123" t="s">
         <v>25</v>
       </c>
       <c r="C123" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D123" t="s">
+        <v>530</v>
+      </c>
+      <c r="E123" t="s">
         <v>531</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
         <v>532</v>
       </c>
-      <c r="F123" t="s">
-        <v>533</v>
-      </c>
       <c r="G123">
-        <v>723</v>
+        <v>609</v>
       </c>
       <c r="H123" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I123" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B124" t="s">
         <v>25</v>
       </c>
       <c r="C124" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D124" t="s">
+        <v>534</v>
+      </c>
+      <c r="E124" t="s">
         <v>535</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>536</v>
       </c>
-      <c r="F124" t="s">
-        <v>537</v>
-      </c>
       <c r="G124">
-        <v>549</v>
+        <v>528</v>
       </c>
       <c r="H124" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I124" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B125" t="s">
         <v>25</v>
       </c>
       <c r="C125" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D125" t="s">
+        <v>538</v>
+      </c>
+      <c r="E125" t="s">
         <v>539</v>
       </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>540</v>
       </c>
-      <c r="F125" t="s">
-        <v>541</v>
-      </c>
       <c r="G125">
-        <v>477</v>
+        <v>714</v>
       </c>
       <c r="H125" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I125" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B126" t="s">
         <v>25</v>
       </c>
       <c r="C126" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D126" t="s">
+        <v>542</v>
+      </c>
+      <c r="E126" t="s">
         <v>543</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>544</v>
       </c>
-      <c r="F126" t="s">
-        <v>545</v>
-      </c>
       <c r="G126">
-        <v>744</v>
+        <v>622</v>
       </c>
       <c r="H126" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I126" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B127" t="s">
         <v>25</v>
       </c>
       <c r="C127" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D127" t="s">
+        <v>546</v>
+      </c>
+      <c r="E127" t="s">
         <v>547</v>
       </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>548</v>
       </c>
-      <c r="F127" t="s">
-        <v>549</v>
-      </c>
       <c r="G127">
-        <v>607</v>
+        <v>317</v>
       </c>
       <c r="H127" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I127" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B128" t="s">
         <v>25</v>
       </c>
       <c r="C128" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D128" t="s">
+        <v>550</v>
+      </c>
+      <c r="E128" t="s">
         <v>551</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>552</v>
       </c>
-      <c r="F128" t="s">
-        <v>553</v>
-      </c>
       <c r="G128">
-        <v>456</v>
+        <v>490</v>
       </c>
       <c r="H128" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I128" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B129" t="s">
         <v>25</v>
       </c>
       <c r="C129" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D129" t="s">
+        <v>554</v>
+      </c>
+      <c r="E129" t="s">
         <v>555</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>556</v>
       </c>
-      <c r="F129" t="s">
-        <v>557</v>
-      </c>
       <c r="G129">
-        <v>771</v>
+        <v>358</v>
       </c>
       <c r="H129" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I129" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B130" t="s">
         <v>25</v>
       </c>
       <c r="C130" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D130" t="s">
+        <v>558</v>
+      </c>
+      <c r="E130" t="s">
         <v>559</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
         <v>560</v>
       </c>
-      <c r="F130" t="s">
-        <v>561</v>
-      </c>
       <c r="G130">
-        <v>429</v>
+        <v>538</v>
       </c>
       <c r="H130" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I130" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B131" t="s">
         <v>25</v>
       </c>
       <c r="C131" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D131" t="s">
+        <v>562</v>
+      </c>
+      <c r="E131" t="s">
         <v>563</v>
       </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
         <v>564</v>
       </c>
-      <c r="F131" t="s">
-        <v>565</v>
-      </c>
       <c r="G131">
-        <v>603</v>
+        <v>502</v>
       </c>
       <c r="H131" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I131" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B132" t="s">
         <v>25</v>
       </c>
       <c r="C132" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D132" t="s">
+        <v>566</v>
+      </c>
+      <c r="E132" t="s">
         <v>567</v>
       </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>568</v>
       </c>
-      <c r="F132" t="s">
-        <v>569</v>
-      </c>
       <c r="G132">
-        <v>384</v>
+        <v>304</v>
       </c>
       <c r="H132" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I132" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B133" t="s">
         <v>25</v>
       </c>
       <c r="C133" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D133" t="s">
+        <v>570</v>
+      </c>
+      <c r="E133" t="s">
         <v>571</v>
       </c>
-      <c r="E133" t="s">
+      <c r="F133" t="s">
         <v>572</v>
       </c>
-      <c r="F133" t="s">
-        <v>573</v>
-      </c>
       <c r="G133">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="H133" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I133" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B134" t="s">
         <v>25</v>
       </c>
       <c r="C134" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D134" t="s">
+        <v>574</v>
+      </c>
+      <c r="E134" t="s">
         <v>575</v>
       </c>
-      <c r="E134" t="s">
+      <c r="F134" t="s">
         <v>576</v>
       </c>
-      <c r="F134" t="s">
-        <v>577</v>
-      </c>
       <c r="G134">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="H134" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I134" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B135" t="s">
         <v>25</v>
       </c>
       <c r="C135" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D135" t="s">
+        <v>578</v>
+      </c>
+      <c r="E135" t="s">
         <v>579</v>
       </c>
-      <c r="E135" t="s">
+      <c r="F135" t="s">
         <v>580</v>
       </c>
-      <c r="F135" t="s">
-        <v>581</v>
-      </c>
       <c r="G135">
-        <v>333</v>
+        <v>682</v>
       </c>
       <c r="H135" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I135" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B136" t="s">
         <v>25</v>
       </c>
       <c r="C136" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D136" t="s">
+        <v>582</v>
+      </c>
+      <c r="E136" t="s">
         <v>583</v>
       </c>
-      <c r="E136" t="s">
+      <c r="F136" t="s">
         <v>584</v>
       </c>
-      <c r="F136" t="s">
-        <v>585</v>
-      </c>
       <c r="G136">
-        <v>714</v>
+        <v>602</v>
       </c>
       <c r="H136" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I136" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B137" t="s">
         <v>25</v>
       </c>
       <c r="C137" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D137" t="s">
+        <v>586</v>
+      </c>
+      <c r="E137" t="s">
         <v>587</v>
       </c>
-      <c r="E137" t="s">
+      <c r="F137" t="s">
         <v>588</v>
       </c>
-      <c r="F137" t="s">
-        <v>589</v>
-      </c>
       <c r="G137">
-        <v>288</v>
+        <v>728</v>
       </c>
       <c r="H137" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I137" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B138" t="s">
         <v>25</v>
       </c>
       <c r="C138" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D138" t="s">
+        <v>590</v>
+      </c>
+      <c r="E138" t="s">
         <v>591</v>
       </c>
-      <c r="E138" t="s">
+      <c r="F138" t="s">
         <v>592</v>
       </c>
-      <c r="F138" t="s">
-        <v>593</v>
-      </c>
       <c r="G138">
-        <v>674</v>
+        <v>413</v>
       </c>
       <c r="H138" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I138" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B139" t="s">
         <v>25</v>
       </c>
       <c r="C139" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D139" t="s">
+        <v>594</v>
+      </c>
+      <c r="E139" t="s">
         <v>595</v>
       </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
         <v>596</v>
       </c>
-      <c r="F139" t="s">
-        <v>597</v>
-      </c>
       <c r="G139">
-        <v>662</v>
+        <v>303</v>
       </c>
       <c r="H139" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I139" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B140" t="s">
         <v>25</v>
       </c>
       <c r="C140" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D140" t="s">
+        <v>598</v>
+      </c>
+      <c r="E140" t="s">
         <v>599</v>
       </c>
-      <c r="E140" t="s">
+      <c r="F140" t="s">
         <v>600</v>
       </c>
-      <c r="F140" t="s">
-        <v>601</v>
-      </c>
       <c r="G140">
-        <v>714</v>
+        <v>745</v>
       </c>
       <c r="H140" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I140" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B141" t="s">
         <v>25</v>
       </c>
       <c r="C141" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D141" t="s">
+        <v>602</v>
+      </c>
+      <c r="E141" t="s">
         <v>603</v>
       </c>
-      <c r="E141" t="s">
+      <c r="F141" t="s">
         <v>604</v>
       </c>
-      <c r="F141" t="s">
-        <v>605</v>
-      </c>
       <c r="G141">
-        <v>266</v>
+        <v>425</v>
       </c>
       <c r="H141" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I141" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B142" t="s">
         <v>25</v>
       </c>
       <c r="C142" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D142" t="s">
+        <v>606</v>
+      </c>
+      <c r="E142" t="s">
         <v>607</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>608</v>
       </c>
-      <c r="F142" t="s">
-        <v>609</v>
-      </c>
       <c r="G142">
-        <v>687</v>
+        <v>577</v>
       </c>
       <c r="H142" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I142" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B143" t="s">
         <v>25</v>
       </c>
       <c r="C143" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D143" t="s">
+        <v>610</v>
+      </c>
+      <c r="E143" t="s">
         <v>611</v>
       </c>
-      <c r="E143" t="s">
+      <c r="F143" t="s">
         <v>612</v>
       </c>
-      <c r="F143" t="s">
-        <v>613</v>
-      </c>
       <c r="G143">
-        <v>535</v>
+        <v>326</v>
       </c>
       <c r="H143" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I143" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B144" t="s">
         <v>25</v>
       </c>
       <c r="C144" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D144" t="s">
+        <v>614</v>
+      </c>
+      <c r="E144" t="s">
         <v>615</v>
       </c>
-      <c r="E144" t="s">
+      <c r="F144" t="s">
         <v>616</v>
       </c>
-      <c r="F144" t="s">
-        <v>617</v>
-      </c>
       <c r="G144">
-        <v>727</v>
+        <v>272</v>
       </c>
       <c r="H144" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I144" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B145" t="s">
         <v>25</v>
       </c>
       <c r="C145" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D145" t="s">
+        <v>618</v>
+      </c>
+      <c r="E145" t="s">
         <v>619</v>
       </c>
-      <c r="E145" t="s">
+      <c r="F145" t="s">
         <v>620</v>
       </c>
-      <c r="F145" t="s">
-        <v>621</v>
-      </c>
       <c r="G145">
-        <v>486</v>
+        <v>364</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I145" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B146" t="s">
         <v>25</v>
       </c>
       <c r="C146" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D146" t="s">
+        <v>622</v>
+      </c>
+      <c r="E146" t="s">
         <v>623</v>
       </c>
-      <c r="E146" t="s">
+      <c r="F146" t="s">
         <v>624</v>
       </c>
-      <c r="F146" t="s">
-        <v>625</v>
-      </c>
       <c r="G146">
-        <v>765</v>
+        <v>266</v>
       </c>
       <c r="H146" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I146" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B147" t="s">
         <v>25</v>
       </c>
       <c r="C147" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D147" t="s">
+        <v>626</v>
+      </c>
+      <c r="E147" t="s">
         <v>627</v>
       </c>
-      <c r="E147" t="s">
+      <c r="F147" t="s">
         <v>628</v>
       </c>
-      <c r="F147" t="s">
-        <v>629</v>
-      </c>
       <c r="G147">
-        <v>795</v>
+        <v>444</v>
       </c>
       <c r="H147" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I147" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B148" t="s">
         <v>25</v>
       </c>
       <c r="C148" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D148" t="s">
+        <v>630</v>
+      </c>
+      <c r="E148" t="s">
         <v>631</v>
       </c>
-      <c r="E148" t="s">
+      <c r="F148" t="s">
         <v>632</v>
       </c>
-      <c r="F148" t="s">
-        <v>633</v>
-      </c>
       <c r="G148">
-        <v>717</v>
+        <v>772</v>
       </c>
       <c r="H148" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I148" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B149" t="s">
         <v>25</v>
       </c>
       <c r="C149" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D149" t="s">
+        <v>634</v>
+      </c>
+      <c r="E149" t="s">
         <v>635</v>
       </c>
-      <c r="E149" t="s">
+      <c r="F149" t="s">
         <v>636</v>
       </c>
-      <c r="F149" t="s">
-        <v>637</v>
-      </c>
       <c r="G149">
-        <v>348</v>
+        <v>588</v>
       </c>
       <c r="H149" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I149" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B150" t="s">
         <v>25</v>
       </c>
       <c r="C150" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D150" t="s">
+        <v>638</v>
+      </c>
+      <c r="E150" t="s">
         <v>639</v>
       </c>
-      <c r="E150" t="s">
+      <c r="F150" t="s">
         <v>640</v>
       </c>
-      <c r="F150" t="s">
-        <v>641</v>
-      </c>
       <c r="G150">
-        <v>583</v>
+        <v>700</v>
       </c>
       <c r="H150" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I150" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B151" t="s">
         <v>25</v>
       </c>
       <c r="C151" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D151" t="s">
+        <v>642</v>
+      </c>
+      <c r="E151" t="s">
         <v>643</v>
       </c>
-      <c r="E151" t="s">
+      <c r="F151" t="s">
         <v>644</v>
       </c>
-      <c r="F151" t="s">
-        <v>645</v>
-      </c>
       <c r="G151">
-        <v>415</v>
+        <v>578</v>
       </c>
       <c r="H151" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I151" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B152" t="s">
         <v>25</v>
       </c>
       <c r="C152" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D152" t="s">
+        <v>646</v>
+      </c>
+      <c r="E152" t="s">
         <v>647</v>
       </c>
-      <c r="E152" t="s">
+      <c r="F152" t="s">
         <v>648</v>
       </c>
-      <c r="F152" t="s">
-        <v>649</v>
-      </c>
       <c r="G152">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="H152" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I152" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B153" t="s">
         <v>25</v>
       </c>
       <c r="C153" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D153" t="s">
+        <v>650</v>
+      </c>
+      <c r="E153" t="s">
         <v>651</v>
       </c>
-      <c r="E153" t="s">
+      <c r="F153" t="s">
         <v>652</v>
       </c>
-      <c r="F153" t="s">
-        <v>653</v>
-      </c>
       <c r="G153">
-        <v>488</v>
+        <v>681</v>
       </c>
       <c r="H153" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I153" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
@@ -8900,7 +8900,7 @@
         <v>25</v>
       </c>
       <c r="C154" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D154" t="s">
         <v>655</v>
@@ -8912,13 +8912,13 @@
         <v>657</v>
       </c>
       <c r="G154">
-        <v>776</v>
+        <v>442</v>
       </c>
       <c r="H154" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I154" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
@@ -8929,7 +8929,7 @@
         <v>25</v>
       </c>
       <c r="C155" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D155" t="s">
         <v>659</v>
@@ -8941,13 +8941,13 @@
         <v>661</v>
       </c>
       <c r="G155">
-        <v>548</v>
+        <v>673</v>
       </c>
       <c r="H155" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I155" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
@@ -8958,7 +8958,7 @@
         <v>25</v>
       </c>
       <c r="C156" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D156" t="s">
         <v>663</v>
@@ -8970,13 +8970,13 @@
         <v>665</v>
       </c>
       <c r="G156">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="H156" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I156" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
@@ -8987,7 +8987,7 @@
         <v>25</v>
       </c>
       <c r="C157" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D157" t="s">
         <v>667</v>
@@ -8999,13 +8999,13 @@
         <v>669</v>
       </c>
       <c r="G157">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="H157" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I157" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
@@ -9016,7 +9016,7 @@
         <v>25</v>
       </c>
       <c r="C158" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D158" t="s">
         <v>671</v>
@@ -9028,13 +9028,13 @@
         <v>673</v>
       </c>
       <c r="G158">
-        <v>594</v>
+        <v>407</v>
       </c>
       <c r="H158" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I158" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
@@ -9045,7 +9045,7 @@
         <v>25</v>
       </c>
       <c r="C159" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D159" t="s">
         <v>675</v>
@@ -9057,13 +9057,13 @@
         <v>677</v>
       </c>
       <c r="G159">
-        <v>592</v>
+        <v>773</v>
       </c>
       <c r="H159" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I159" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
@@ -9074,7 +9074,7 @@
         <v>25</v>
       </c>
       <c r="C160" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D160" t="s">
         <v>679</v>
@@ -9086,13 +9086,13 @@
         <v>681</v>
       </c>
       <c r="G160">
-        <v>315</v>
+        <v>713</v>
       </c>
       <c r="H160" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I160" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
@@ -9103,7 +9103,7 @@
         <v>25</v>
       </c>
       <c r="C161" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D161" t="s">
         <v>683</v>
@@ -9115,13 +9115,13 @@
         <v>685</v>
       </c>
       <c r="G161">
-        <v>427</v>
+        <v>341</v>
       </c>
       <c r="H161" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I161" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
@@ -9144,13 +9144,13 @@
         <v>690</v>
       </c>
       <c r="G162">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="H162" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I162" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
@@ -9173,13 +9173,13 @@
         <v>694</v>
       </c>
       <c r="G163">
-        <v>70</v>
+        <v>248</v>
       </c>
       <c r="H163" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I163" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
@@ -9202,13 +9202,13 @@
         <v>698</v>
       </c>
       <c r="G164">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="H164" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I164" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
@@ -9231,13 +9231,13 @@
         <v>702</v>
       </c>
       <c r="G165">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="H165" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I165" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
@@ -9260,13 +9260,13 @@
         <v>706</v>
       </c>
       <c r="G166">
-        <v>233</v>
+        <v>132</v>
       </c>
       <c r="H166" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I166" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
@@ -9289,13 +9289,13 @@
         <v>710</v>
       </c>
       <c r="G167">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="H167" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I167" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
@@ -9318,13 +9318,13 @@
         <v>714</v>
       </c>
       <c r="G168">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="H168" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I168" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
@@ -9347,13 +9347,13 @@
         <v>718</v>
       </c>
       <c r="G169">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="H169" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I169" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
@@ -9376,13 +9376,13 @@
         <v>722</v>
       </c>
       <c r="G170">
-        <v>117</v>
+        <v>205</v>
       </c>
       <c r="H170" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I170" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
@@ -9405,13 +9405,13 @@
         <v>726</v>
       </c>
       <c r="G171">
-        <v>227</v>
+        <v>57</v>
       </c>
       <c r="H171" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I171" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
@@ -9434,13 +9434,13 @@
         <v>730</v>
       </c>
       <c r="G172">
-        <v>207</v>
+        <v>65</v>
       </c>
       <c r="H172" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I172" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
@@ -9463,13 +9463,13 @@
         <v>734</v>
       </c>
       <c r="G173">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H173" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I173" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
@@ -9492,13 +9492,13 @@
         <v>738</v>
       </c>
       <c r="G174">
-        <v>217</v>
+        <v>98</v>
       </c>
       <c r="H174" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I174" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
@@ -9521,13 +9521,13 @@
         <v>742</v>
       </c>
       <c r="G175">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="H175" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I175" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
@@ -9550,13 +9550,13 @@
         <v>746</v>
       </c>
       <c r="G176">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="H176" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I176" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
@@ -9579,13 +9579,13 @@
         <v>750</v>
       </c>
       <c r="G177">
-        <v>212</v>
+        <v>117</v>
       </c>
       <c r="H177" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I177" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
@@ -9608,13 +9608,13 @@
         <v>754</v>
       </c>
       <c r="G178">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="H178" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I178" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
@@ -9637,13 +9637,13 @@
         <v>758</v>
       </c>
       <c r="G179">
-        <v>123</v>
+        <v>195</v>
       </c>
       <c r="H179" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I179" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
@@ -9666,13 +9666,13 @@
         <v>762</v>
       </c>
       <c r="G180">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="H180" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I180" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
@@ -9695,13 +9695,13 @@
         <v>766</v>
       </c>
       <c r="G181">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H181" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I181" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
@@ -9724,13 +9724,13 @@
         <v>770</v>
       </c>
       <c r="G182">
-        <v>247</v>
+        <v>183</v>
       </c>
       <c r="H182" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I182" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
@@ -9753,13 +9753,13 @@
         <v>774</v>
       </c>
       <c r="G183">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="H183" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I183" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
@@ -9782,13 +9782,13 @@
         <v>778</v>
       </c>
       <c r="G184">
-        <v>135</v>
+        <v>56</v>
       </c>
       <c r="H184" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I184" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
@@ -9811,13 +9811,13 @@
         <v>782</v>
       </c>
       <c r="G185">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="H185" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I185" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
@@ -9840,13 +9840,13 @@
         <v>786</v>
       </c>
       <c r="G186">
-        <v>140</v>
+        <v>56</v>
       </c>
       <c r="H186" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I186" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
@@ -9869,13 +9869,13 @@
         <v>790</v>
       </c>
       <c r="G187">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="H187" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I187" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
@@ -9898,13 +9898,13 @@
         <v>794</v>
       </c>
       <c r="G188">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H188" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I188" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
@@ -9927,13 +9927,13 @@
         <v>798</v>
       </c>
       <c r="G189">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="H189" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I189" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
@@ -9956,13 +9956,13 @@
         <v>802</v>
       </c>
       <c r="G190">
-        <v>65</v>
+        <v>145</v>
       </c>
       <c r="H190" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I190" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
@@ -9985,13 +9985,13 @@
         <v>806</v>
       </c>
       <c r="G191">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="H191" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I191" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
@@ -10014,13 +10014,13 @@
         <v>810</v>
       </c>
       <c r="G192">
-        <v>223</v>
+        <v>94</v>
       </c>
       <c r="H192" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I192" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
@@ -10043,13 +10043,13 @@
         <v>814</v>
       </c>
       <c r="G193">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="H193" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I193" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
@@ -10072,13 +10072,13 @@
         <v>818</v>
       </c>
       <c r="G194">
-        <v>197</v>
+        <v>64</v>
       </c>
       <c r="H194" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I194" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
@@ -10101,13 +10101,13 @@
         <v>822</v>
       </c>
       <c r="G195">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="H195" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I195" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
@@ -10130,13 +10130,13 @@
         <v>826</v>
       </c>
       <c r="G196">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H196" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I196" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
@@ -10159,13 +10159,13 @@
         <v>830</v>
       </c>
       <c r="G197">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="H197" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I197" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
@@ -10188,13 +10188,13 @@
         <v>834</v>
       </c>
       <c r="G198">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H198" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I198" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
@@ -10217,13 +10217,13 @@
         <v>838</v>
       </c>
       <c r="G199">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="H199" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I199" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
@@ -10246,13 +10246,13 @@
         <v>842</v>
       </c>
       <c r="G200">
-        <v>199</v>
+        <v>148</v>
       </c>
       <c r="H200" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I200" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
@@ -10275,13 +10275,13 @@
         <v>846</v>
       </c>
       <c r="G201">
-        <v>163</v>
+        <v>60</v>
       </c>
       <c r="H201" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I201" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
@@ -10304,13 +10304,13 @@
         <v>850</v>
       </c>
       <c r="G202">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="H202" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I202" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
@@ -10333,13 +10333,13 @@
         <v>854</v>
       </c>
       <c r="G203">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="H203" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I203" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
@@ -10362,13 +10362,13 @@
         <v>858</v>
       </c>
       <c r="G204">
-        <v>225</v>
+        <v>139</v>
       </c>
       <c r="H204" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I204" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
@@ -10391,13 +10391,13 @@
         <v>862</v>
       </c>
       <c r="G205">
-        <v>65</v>
+        <v>174</v>
       </c>
       <c r="H205" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I205" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
@@ -10420,13 +10420,13 @@
         <v>866</v>
       </c>
       <c r="G206">
-        <v>169</v>
+        <v>239</v>
       </c>
       <c r="H206" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I206" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
@@ -10449,13 +10449,13 @@
         <v>870</v>
       </c>
       <c r="G207">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="H207" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I207" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
@@ -10478,13 +10478,13 @@
         <v>874</v>
       </c>
       <c r="G208">
-        <v>87</v>
+        <v>241</v>
       </c>
       <c r="H208" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I208" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
@@ -10507,13 +10507,13 @@
         <v>878</v>
       </c>
       <c r="G209">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="H209" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I209" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
@@ -10536,13 +10536,13 @@
         <v>882</v>
       </c>
       <c r="G210">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="H210" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I210" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
@@ -10565,13 +10565,13 @@
         <v>886</v>
       </c>
       <c r="G211">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H211" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I211" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
@@ -10594,13 +10594,13 @@
         <v>890</v>
       </c>
       <c r="G212">
-        <v>114</v>
+        <v>57</v>
       </c>
       <c r="H212" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I212" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
@@ -10623,13 +10623,13 @@
         <v>894</v>
       </c>
       <c r="G213">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="H213" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I213" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
@@ -10652,13 +10652,13 @@
         <v>898</v>
       </c>
       <c r="G214">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="H214" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I214" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
@@ -10681,13 +10681,13 @@
         <v>902</v>
       </c>
       <c r="G215">
-        <v>246</v>
+        <v>198</v>
       </c>
       <c r="H215" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I215" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
@@ -10710,13 +10710,13 @@
         <v>906</v>
       </c>
       <c r="G216">
-        <v>123</v>
+        <v>52</v>
       </c>
       <c r="H216" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I216" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
@@ -10739,13 +10739,13 @@
         <v>910</v>
       </c>
       <c r="G217">
-        <v>137</v>
+        <v>50</v>
       </c>
       <c r="H217" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I217" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
@@ -10768,13 +10768,13 @@
         <v>914</v>
       </c>
       <c r="G218">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="H218" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I218" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
@@ -10797,13 +10797,13 @@
         <v>918</v>
       </c>
       <c r="G219">
-        <v>81</v>
+        <v>228</v>
       </c>
       <c r="H219" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I219" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
@@ -10826,13 +10826,13 @@
         <v>922</v>
       </c>
       <c r="G220">
-        <v>246</v>
+        <v>168</v>
       </c>
       <c r="H220" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I220" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
@@ -10855,13 +10855,13 @@
         <v>926</v>
       </c>
       <c r="G221">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="H221" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I221" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
@@ -10884,13 +10884,13 @@
         <v>931</v>
       </c>
       <c r="G222">
-        <v>286</v>
+        <v>328</v>
       </c>
       <c r="H222" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I222" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
@@ -10913,13 +10913,13 @@
         <v>935</v>
       </c>
       <c r="G223">
-        <v>394</v>
+        <v>468</v>
       </c>
       <c r="H223" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I223" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
@@ -10942,13 +10942,13 @@
         <v>939</v>
       </c>
       <c r="G224">
-        <v>349</v>
+        <v>484</v>
       </c>
       <c r="H224" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I224" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
@@ -10971,13 +10971,13 @@
         <v>943</v>
       </c>
       <c r="G225">
-        <v>506</v>
+        <v>565</v>
       </c>
       <c r="H225" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I225" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
@@ -11000,13 +11000,13 @@
         <v>947</v>
       </c>
       <c r="G226">
-        <v>218</v>
+        <v>301</v>
       </c>
       <c r="H226" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I226" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
@@ -11029,13 +11029,13 @@
         <v>951</v>
       </c>
       <c r="G227">
-        <v>369</v>
+        <v>420</v>
       </c>
       <c r="H227" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I227" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
@@ -11058,13 +11058,13 @@
         <v>955</v>
       </c>
       <c r="G228">
-        <v>496</v>
+        <v>300</v>
       </c>
       <c r="H228" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I228" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
@@ -11087,13 +11087,13 @@
         <v>959</v>
       </c>
       <c r="G229">
-        <v>264</v>
+        <v>205</v>
       </c>
       <c r="H229" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I229" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
@@ -11116,13 +11116,13 @@
         <v>963</v>
       </c>
       <c r="G230">
-        <v>271</v>
+        <v>208</v>
       </c>
       <c r="H230" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I230" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
@@ -11145,13 +11145,13 @@
         <v>967</v>
       </c>
       <c r="G231">
-        <v>286</v>
+        <v>497</v>
       </c>
       <c r="H231" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I231" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
@@ -11174,13 +11174,13 @@
         <v>971</v>
       </c>
       <c r="G232">
-        <v>572</v>
+        <v>442</v>
       </c>
       <c r="H232" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I232" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
@@ -11203,13 +11203,13 @@
         <v>975</v>
       </c>
       <c r="G233">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H233" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I233" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
@@ -11232,13 +11232,13 @@
         <v>979</v>
       </c>
       <c r="G234">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="H234" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I234" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
@@ -11261,13 +11261,13 @@
         <v>983</v>
       </c>
       <c r="G235">
-        <v>540</v>
+        <v>461</v>
       </c>
       <c r="H235" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I235" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
@@ -11290,13 +11290,13 @@
         <v>987</v>
       </c>
       <c r="G236">
-        <v>221</v>
+        <v>476</v>
       </c>
       <c r="H236" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I236" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
@@ -11319,13 +11319,13 @@
         <v>991</v>
       </c>
       <c r="G237">
-        <v>595</v>
+        <v>554</v>
       </c>
       <c r="H237" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I237" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
@@ -11348,13 +11348,13 @@
         <v>995</v>
       </c>
       <c r="G238">
-        <v>577</v>
+        <v>502</v>
       </c>
       <c r="H238" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I238" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
@@ -11377,13 +11377,13 @@
         <v>999</v>
       </c>
       <c r="G239">
-        <v>216</v>
+        <v>441</v>
       </c>
       <c r="H239" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I239" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
@@ -11406,13 +11406,13 @@
         <v>1003</v>
       </c>
       <c r="G240">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H240" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I240" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
@@ -11435,13 +11435,13 @@
         <v>1007</v>
       </c>
       <c r="G241">
-        <v>548</v>
+        <v>386</v>
       </c>
       <c r="H241" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I241" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
@@ -11464,13 +11464,13 @@
         <v>1011</v>
       </c>
       <c r="G242">
-        <v>291</v>
+        <v>532</v>
       </c>
       <c r="H242" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I242" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
@@ -11493,13 +11493,13 @@
         <v>1015</v>
       </c>
       <c r="G243">
-        <v>341</v>
+        <v>235</v>
       </c>
       <c r="H243" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I243" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
@@ -11522,13 +11522,13 @@
         <v>1019</v>
       </c>
       <c r="G244">
-        <v>459</v>
+        <v>385</v>
       </c>
       <c r="H244" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I244" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
@@ -11551,13 +11551,13 @@
         <v>1023</v>
       </c>
       <c r="G245">
-        <v>266</v>
+        <v>564</v>
       </c>
       <c r="H245" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I245" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
@@ -11580,13 +11580,13 @@
         <v>1027</v>
       </c>
       <c r="G246">
-        <v>318</v>
+        <v>212</v>
       </c>
       <c r="H246" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I246" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
@@ -11609,13 +11609,13 @@
         <v>1031</v>
       </c>
       <c r="G247">
-        <v>591</v>
+        <v>517</v>
       </c>
       <c r="H247" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I247" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
@@ -11638,13 +11638,13 @@
         <v>1035</v>
       </c>
       <c r="G248">
-        <v>502</v>
+        <v>412</v>
       </c>
       <c r="H248" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I248" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
@@ -11667,13 +11667,13 @@
         <v>1039</v>
       </c>
       <c r="G249">
-        <v>424</v>
+        <v>478</v>
       </c>
       <c r="H249" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I249" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
@@ -11696,13 +11696,13 @@
         <v>1043</v>
       </c>
       <c r="G250">
-        <v>429</v>
+        <v>248</v>
       </c>
       <c r="H250" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I250" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
@@ -11725,13 +11725,13 @@
         <v>1047</v>
       </c>
       <c r="G251">
-        <v>482</v>
+        <v>374</v>
       </c>
       <c r="H251" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I251" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
@@ -11754,13 +11754,13 @@
         <v>1051</v>
       </c>
       <c r="G252">
-        <v>299</v>
+        <v>261</v>
       </c>
       <c r="H252" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I252" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
@@ -11783,13 +11783,13 @@
         <v>1055</v>
       </c>
       <c r="G253">
-        <v>476</v>
+        <v>245</v>
       </c>
       <c r="H253" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I253" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
@@ -11812,13 +11812,13 @@
         <v>1059</v>
       </c>
       <c r="G254">
-        <v>443</v>
+        <v>296</v>
       </c>
       <c r="H254" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I254" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
@@ -11841,13 +11841,13 @@
         <v>1063</v>
       </c>
       <c r="G255">
-        <v>514</v>
+        <v>487</v>
       </c>
       <c r="H255" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I255" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
@@ -11870,13 +11870,13 @@
         <v>1067</v>
       </c>
       <c r="G256">
-        <v>388</v>
+        <v>344</v>
       </c>
       <c r="H256" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I256" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
@@ -11899,13 +11899,13 @@
         <v>1071</v>
       </c>
       <c r="G257">
-        <v>524</v>
+        <v>410</v>
       </c>
       <c r="H257" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I257" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
@@ -11928,13 +11928,13 @@
         <v>1075</v>
       </c>
       <c r="G258">
-        <v>208</v>
+        <v>500</v>
       </c>
       <c r="H258" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I258" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
@@ -11957,13 +11957,13 @@
         <v>1079</v>
       </c>
       <c r="G259">
-        <v>418</v>
+        <v>369</v>
       </c>
       <c r="H259" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I259" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
@@ -11986,13 +11986,13 @@
         <v>1083</v>
       </c>
       <c r="G260">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="H260" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I260" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
@@ -12015,13 +12015,13 @@
         <v>1087</v>
       </c>
       <c r="G261">
-        <v>463</v>
+        <v>537</v>
       </c>
       <c r="H261" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I261" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
@@ -12044,13 +12044,13 @@
         <v>1091</v>
       </c>
       <c r="G262">
-        <v>389</v>
+        <v>211</v>
       </c>
       <c r="H262" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I262" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
@@ -12073,13 +12073,13 @@
         <v>1095</v>
       </c>
       <c r="G263">
-        <v>321</v>
+        <v>237</v>
       </c>
       <c r="H263" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I263" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
@@ -12102,13 +12102,13 @@
         <v>1099</v>
       </c>
       <c r="G264">
-        <v>579</v>
+        <v>417</v>
       </c>
       <c r="H264" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I264" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
@@ -12131,13 +12131,13 @@
         <v>1103</v>
       </c>
       <c r="G265">
-        <v>336</v>
+        <v>464</v>
       </c>
       <c r="H265" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I265" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
@@ -12160,13 +12160,13 @@
         <v>1107</v>
       </c>
       <c r="G266">
-        <v>366</v>
+        <v>277</v>
       </c>
       <c r="H266" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I266" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
@@ -12195,7 +12195,7 @@
         <v>46</v>
       </c>
       <c r="I267" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
@@ -12218,13 +12218,13 @@
         <v>1115</v>
       </c>
       <c r="G268">
-        <v>397</v>
+        <v>309</v>
       </c>
       <c r="H268" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I268" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
@@ -12247,13 +12247,13 @@
         <v>1119</v>
       </c>
       <c r="G269">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="H269" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I269" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
@@ -12276,13 +12276,13 @@
         <v>1123</v>
       </c>
       <c r="G270">
-        <v>494</v>
+        <v>593</v>
       </c>
       <c r="H270" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I270" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
@@ -12305,13 +12305,13 @@
         <v>1127</v>
       </c>
       <c r="G271">
-        <v>536</v>
+        <v>205</v>
       </c>
       <c r="H271" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I271" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
@@ -12334,13 +12334,13 @@
         <v>1132</v>
       </c>
       <c r="G272">
-        <v>320</v>
+        <v>118</v>
       </c>
       <c r="H272" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I272" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
@@ -12363,13 +12363,13 @@
         <v>1136</v>
       </c>
       <c r="G273">
-        <v>100</v>
+        <v>191</v>
       </c>
       <c r="H273" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I273" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
@@ -12392,13 +12392,13 @@
         <v>1140</v>
       </c>
       <c r="G274">
-        <v>293</v>
+        <v>176</v>
       </c>
       <c r="H274" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I274" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
@@ -12421,13 +12421,13 @@
         <v>1144</v>
       </c>
       <c r="G275">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="H275" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I275" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
@@ -12450,13 +12450,13 @@
         <v>1148</v>
       </c>
       <c r="G276">
-        <v>142</v>
+        <v>323</v>
       </c>
       <c r="H276" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I276" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
@@ -12479,13 +12479,13 @@
         <v>1152</v>
       </c>
       <c r="G277">
-        <v>182</v>
+        <v>261</v>
       </c>
       <c r="H277" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I277" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
@@ -12508,13 +12508,13 @@
         <v>1156</v>
       </c>
       <c r="G278">
-        <v>288</v>
+        <v>231</v>
       </c>
       <c r="H278" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I278" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
@@ -12537,13 +12537,13 @@
         <v>1160</v>
       </c>
       <c r="G279">
-        <v>261</v>
+        <v>213</v>
       </c>
       <c r="H279" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I279" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
@@ -12566,13 +12566,13 @@
         <v>1164</v>
       </c>
       <c r="G280">
-        <v>152</v>
+        <v>265</v>
       </c>
       <c r="H280" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I280" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
@@ -12595,13 +12595,13 @@
         <v>1168</v>
       </c>
       <c r="G281">
-        <v>205</v>
+        <v>344</v>
       </c>
       <c r="H281" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I281" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
@@ -12624,13 +12624,13 @@
         <v>1172</v>
       </c>
       <c r="G282">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="H282" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I282" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
@@ -12653,13 +12653,13 @@
         <v>1176</v>
       </c>
       <c r="G283">
-        <v>325</v>
+        <v>279</v>
       </c>
       <c r="H283" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I283" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
@@ -12682,13 +12682,13 @@
         <v>1180</v>
       </c>
       <c r="G284">
-        <v>186</v>
+        <v>293</v>
       </c>
       <c r="H284" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I284" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
@@ -12711,13 +12711,13 @@
         <v>1184</v>
       </c>
       <c r="G285">
-        <v>222</v>
+        <v>168</v>
       </c>
       <c r="H285" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I285" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
@@ -12740,13 +12740,13 @@
         <v>1188</v>
       </c>
       <c r="G286">
-        <v>102</v>
+        <v>296</v>
       </c>
       <c r="H286" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I286" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
@@ -12769,13 +12769,13 @@
         <v>1192</v>
       </c>
       <c r="G287">
-        <v>221</v>
+        <v>100</v>
       </c>
       <c r="H287" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I287" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
@@ -12798,13 +12798,13 @@
         <v>1196</v>
       </c>
       <c r="G288">
-        <v>283</v>
+        <v>160</v>
       </c>
       <c r="H288" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I288" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.25">
@@ -12827,13 +12827,13 @@
         <v>1200</v>
       </c>
       <c r="G289">
-        <v>188</v>
+        <v>342</v>
       </c>
       <c r="H289" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I289" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
@@ -12856,13 +12856,13 @@
         <v>1204</v>
       </c>
       <c r="G290">
-        <v>289</v>
+        <v>198</v>
       </c>
       <c r="H290" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I290" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
@@ -12885,13 +12885,13 @@
         <v>1208</v>
       </c>
       <c r="G291">
-        <v>295</v>
+        <v>340</v>
       </c>
       <c r="H291" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I291" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.25">
@@ -12914,13 +12914,13 @@
         <v>1212</v>
       </c>
       <c r="G292">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H292" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I292" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
@@ -12943,13 +12943,13 @@
         <v>1216</v>
       </c>
       <c r="G293">
-        <v>283</v>
+        <v>251</v>
       </c>
       <c r="H293" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I293" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
@@ -12972,13 +12972,13 @@
         <v>1220</v>
       </c>
       <c r="G294">
-        <v>272</v>
+        <v>141</v>
       </c>
       <c r="H294" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I294" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
@@ -13001,13 +13001,13 @@
         <v>1224</v>
       </c>
       <c r="G295">
-        <v>224</v>
+        <v>164</v>
       </c>
       <c r="H295" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I295" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
@@ -13030,13 +13030,13 @@
         <v>1228</v>
       </c>
       <c r="G296">
-        <v>212</v>
+        <v>319</v>
       </c>
       <c r="H296" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I296" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
@@ -13059,13 +13059,13 @@
         <v>1232</v>
       </c>
       <c r="G297">
-        <v>191</v>
+        <v>296</v>
       </c>
       <c r="H297" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I297" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
@@ -13088,13 +13088,13 @@
         <v>1236</v>
       </c>
       <c r="G298">
-        <v>237</v>
+        <v>320</v>
       </c>
       <c r="H298" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I298" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
@@ -13117,13 +13117,13 @@
         <v>1240</v>
       </c>
       <c r="G299">
-        <v>318</v>
+        <v>221</v>
       </c>
       <c r="H299" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I299" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
@@ -13146,13 +13146,13 @@
         <v>1244</v>
       </c>
       <c r="G300">
-        <v>186</v>
+        <v>124</v>
       </c>
       <c r="H300" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I300" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
@@ -13175,13 +13175,13 @@
         <v>1248</v>
       </c>
       <c r="G301">
-        <v>132</v>
+        <v>245</v>
       </c>
       <c r="H301" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I301" t="s">
-        <v>52</v>
+        <v>653</v>
       </c>
     </row>
   </sheetData>
